--- a/database/event/7904/event_7904_evp_summary.xlsx
+++ b/database/event/7904/event_7904_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>11.557</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7.5366</v>
       </c>
       <c r="D2" t="n">
         <v>4.2474</v>
@@ -545,7 +545,7 @@
         <v>9.056800000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5.9061</v>
       </c>
       <c r="D3" t="n">
         <v>3.2374</v>
@@ -591,7 +591,7 @@
         <v>7.1437</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.6586</v>
       </c>
       <c r="D4" t="n">
         <v>2.4645</v>
@@ -637,7 +637,7 @@
         <v>6.6822</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4.3576</v>
       </c>
       <c r="D5" t="n">
         <v>2.2781</v>
@@ -683,7 +683,7 @@
         <v>5.552</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.6206</v>
       </c>
       <c r="D6" t="n">
         <v>1.8215</v>
@@ -729,7 +729,7 @@
         <v>5.0904</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.3196</v>
       </c>
       <c r="D7" t="n">
         <v>1.635</v>
@@ -775,7 +775,7 @@
         <v>5.0563</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3.2973</v>
       </c>
       <c r="D8" t="n">
         <v>1.6213</v>
@@ -821,7 +821,7 @@
         <v>4.5134</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.9433</v>
       </c>
       <c r="D9" t="n">
         <v>1.402</v>
@@ -867,7 +867,7 @@
         <v>3.7887</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.4707</v>
       </c>
       <c r="D10" t="n">
         <v>1.1092</v>
@@ -913,7 +913,7 @@
         <v>3.6411</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.3744</v>
       </c>
       <c r="D11" t="n">
         <v>1.0496</v>
@@ -959,7 +959,7 @@
         <v>3.4776</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.2678</v>
       </c>
       <c r="D12" t="n">
         <v>0.9835</v>
@@ -1005,7 +1005,7 @@
         <v>3.4204</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.2305</v>
       </c>
       <c r="D13" t="n">
         <v>0.9604</v>
@@ -1051,7 +1051,7 @@
         <v>3.2504</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.1197</v>
       </c>
       <c r="D14" t="n">
         <v>0.8917</v>
@@ -1097,7 +1097,7 @@
         <v>3.1253</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2.0381</v>
       </c>
       <c r="D15" t="n">
         <v>0.8411999999999999</v>
@@ -1143,7 +1143,7 @@
         <v>2.681</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.7483</v>
       </c>
       <c r="D16" t="n">
         <v>0.6617</v>
@@ -1189,7 +1189,7 @@
         <v>2.4906</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.6242</v>
       </c>
       <c r="D17" t="n">
         <v>0.5848</v>
@@ -1235,7 +1235,7 @@
         <v>2.4132</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.5737</v>
       </c>
       <c r="D18" t="n">
         <v>0.5535</v>
@@ -1281,7 +1281,7 @@
         <v>2.3482</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.5313</v>
       </c>
       <c r="D19" t="n">
         <v>0.5273</v>
@@ -1327,7 +1327,7 @@
         <v>2.2642</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.4765</v>
       </c>
       <c r="D20" t="n">
         <v>0.4933</v>
@@ -1373,7 +1373,7 @@
         <v>2.2543</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.4701</v>
       </c>
       <c r="D21" t="n">
         <v>0.4893</v>
@@ -1419,7 +1419,7 @@
         <v>2.128</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.3877</v>
       </c>
       <c r="D22" t="n">
         <v>0.4383</v>
@@ -1465,7 +1465,7 @@
         <v>2.0921</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.3643</v>
       </c>
       <c r="D23" t="n">
         <v>0.4238</v>
@@ -1511,7 +1511,7 @@
         <v>2.0863</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.3605</v>
       </c>
       <c r="D24" t="n">
         <v>0.4215</v>
@@ -1557,7 +1557,7 @@
         <v>1.9857</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.2949</v>
       </c>
       <c r="D25" t="n">
         <v>0.3808</v>
@@ -1603,7 +1603,7 @@
         <v>1.9838</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.2937</v>
       </c>
       <c r="D26" t="n">
         <v>0.38</v>
@@ -1649,7 +1649,7 @@
         <v>1.9145</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.2485</v>
       </c>
       <c r="D27" t="n">
         <v>0.3521</v>
@@ -1695,7 +1695,7 @@
         <v>1.68</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.0956</v>
       </c>
       <c r="D28" t="n">
         <v>0.2573</v>
@@ -1741,7 +1741,7 @@
         <v>1.6684</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1.088</v>
       </c>
       <c r="D29" t="n">
         <v>0.2526</v>
@@ -1787,7 +1787,7 @@
         <v>1.6075</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.0483</v>
       </c>
       <c r="D30" t="n">
         <v>0.228</v>
@@ -1833,7 +1833,7 @@
         <v>1.6024</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1.045</v>
       </c>
       <c r="D31" t="n">
         <v>0.226</v>
@@ -1879,7 +1879,7 @@
         <v>1.5803</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1.0305</v>
       </c>
       <c r="D32" t="n">
         <v>0.217</v>
@@ -1925,7 +1925,7 @@
         <v>1.5051</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.9815</v>
       </c>
       <c r="D33" t="n">
         <v>0.1867</v>
@@ -1971,7 +1971,7 @@
         <v>1.4179</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.9246</v>
       </c>
       <c r="D34" t="n">
         <v>0.1514</v>
@@ -2017,7 +2017,7 @@
         <v>1.2205</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="D35" t="n">
         <v>0.0717</v>
@@ -2063,7 +2063,7 @@
         <v>1.1665</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.7607</v>
       </c>
       <c r="D36" t="n">
         <v>0.0499</v>
@@ -2109,7 +2109,7 @@
         <v>1.0575</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.6896</v>
       </c>
       <c r="D37" t="n">
         <v>0.0058</v>
@@ -2155,7 +2155,7 @@
         <v>1.0143</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.6614</v>
       </c>
       <c r="D38" t="n">
         <v>-0.0116</v>
@@ -2201,7 +2201,7 @@
         <v>0.9518</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.6207</v>
       </c>
       <c r="D39" t="n">
         <v>-0.0369</v>
@@ -2247,7 +2247,7 @@
         <v>0.8963</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.5845</v>
       </c>
       <c r="D40" t="n">
         <v>-0.0593</v>
@@ -2293,7 +2293,7 @@
         <v>0.7826</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.5104</v>
       </c>
       <c r="D41" t="n">
         <v>-0.1052</v>
@@ -2339,7 +2339,7 @@
         <v>0.4067</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.2652</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2571</v>
@@ -2385,7 +2385,7 @@
         <v>0.3614</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2357</v>
       </c>
       <c r="D43" t="n">
         <v>-0.2754</v>
@@ -2431,7 +2431,7 @@
         <v>0.3595</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2344</v>
       </c>
       <c r="D44" t="n">
         <v>-0.2761</v>
@@ -2477,7 +2477,7 @@
         <v>0.334</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.2178</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2864</v>
@@ -2523,7 +2523,7 @@
         <v>0.2455</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1601</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3222</v>
@@ -2569,7 +2569,7 @@
         <v>0.1606</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.1047</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3565</v>
@@ -2615,7 +2615,7 @@
         <v>0.1519</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>-0.36</v>
@@ -2661,7 +2661,7 @@
         <v>0.0975</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.0636</v>
       </c>
       <c r="D49" t="n">
         <v>-0.382</v>
@@ -2707,7 +2707,7 @@
         <v>0.0364</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.0237</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4067</v>
@@ -2753,7 +2753,7 @@
         <v>-0.1012</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.066</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4622</v>
@@ -2799,7 +2799,7 @@
         <v>-0.1543</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.1006</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4837</v>
@@ -2845,7 +2845,7 @@
         <v>-0.1894</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1235</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4979</v>
@@ -2891,7 +2891,7 @@
         <v>-0.2324</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1516</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5152</v>
@@ -2937,7 +2937,7 @@
         <v>-0.248</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1617</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5215</v>
@@ -2983,7 +2983,7 @@
         <v>-0.2483</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1619</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5217000000000001</v>
@@ -3029,7 +3029,7 @@
         <v>-0.286</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.1865</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5369</v>
@@ -3075,7 +3075,7 @@
         <v>-0.3645</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2377</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5686</v>
@@ -3121,7 +3121,7 @@
         <v>-0.4502</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2936</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6032</v>
@@ -3167,7 +3167,7 @@
         <v>-0.5306999999999999</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.3461</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6358</v>
@@ -3213,7 +3213,7 @@
         <v>-0.5327</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.3474</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6366000000000001</v>
@@ -3259,7 +3259,7 @@
         <v>-0.5479000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3573</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6427</v>
@@ -3305,7 +3305,7 @@
         <v>-0.6394</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.417</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6797</v>
@@ -3351,7 +3351,7 @@
         <v>-0.7341</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.4787</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7179</v>
@@ -3397,7 +3397,7 @@
         <v>-0.7931</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.5172</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7418</v>
@@ -3443,7 +3443,7 @@
         <v>-0.9482</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.6183</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8044</v>
@@ -3489,7 +3489,7 @@
         <v>-0.975</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.6358</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8152</v>
@@ -3535,7 +3535,7 @@
         <v>-1.2273</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.8003</v>
       </c>
       <c r="D68" t="n">
         <v>-0.9172</v>
@@ -3581,7 +3581,7 @@
         <v>-1.2498</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="D69" t="n">
         <v>-0.9263</v>
@@ -3627,7 +3627,7 @@
         <v>-1.2513</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9268999999999999</v>
@@ -3673,7 +3673,7 @@
         <v>-1.3161</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.8583</v>
       </c>
       <c r="D71" t="n">
         <v>-0.953</v>
@@ -3719,7 +3719,7 @@
         <v>-1.5651</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-1.0206</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0536</v>
@@ -3765,7 +3765,7 @@
         <v>-1.6013</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-1.0442</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0683</v>
@@ -3811,7 +3811,7 @@
         <v>-1.603</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-1.0454</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0689</v>
@@ -3857,7 +3857,7 @@
         <v>-1.6105</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.0502</v>
       </c>
       <c r="D75" t="n">
         <v>-1.072</v>
@@ -3903,7 +3903,7 @@
         <v>-1.6547</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.0791</v>
       </c>
       <c r="D76" t="n">
         <v>-1.0898</v>
@@ -3949,7 +3949,7 @@
         <v>-1.7531</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.1432</v>
       </c>
       <c r="D77" t="n">
         <v>-1.1296</v>
@@ -3995,7 +3995,7 @@
         <v>-1.8256</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.1905</v>
       </c>
       <c r="D78" t="n">
         <v>-1.1589</v>
@@ -4041,7 +4041,7 @@
         <v>-2</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.3042</v>
       </c>
       <c r="D79" t="n">
         <v>-1.2293</v>
@@ -4087,7 +4087,7 @@
         <v>-2</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.3042</v>
       </c>
       <c r="D80" t="n">
         <v>-1.2293</v>
@@ -4133,7 +4133,7 @@
         <v>-3.8647</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.5203</v>
       </c>
       <c r="D81" t="n">
         <v>-1.9826</v>

--- a/database/event/7904/event_7904_evp_summary.xlsx
+++ b/database/event/7904/event_7904_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>7.5366</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2474</v>
+        <v>4.1604</v>
       </c>
       <c r="E2" t="n">
         <v>11.557</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.056800000000001</v>
+        <v>9.020899999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9061</v>
+        <v>5.8827</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2374</v>
+        <v>3.15</v>
       </c>
       <c r="E3" t="n">
-        <v>9.056800000000001</v>
+        <v>9.020899999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6878</v>
+        <v>4.6519</v>
       </c>
       <c r="G3" t="n">
         <v>4.369</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0474</v>
+        <v>4.9911</v>
       </c>
       <c r="I3" t="n">
         <v>5.1182</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.1437</v>
+        <v>7.111</v>
       </c>
       <c r="C4" t="n">
-        <v>4.6586</v>
+        <v>4.6372</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4645</v>
+        <v>2.3891</v>
       </c>
       <c r="E4" t="n">
-        <v>7.1437</v>
+        <v>7.111</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3986</v>
+        <v>4.366</v>
       </c>
       <c r="G4" t="n">
         <v>2.745</v>
       </c>
       <c r="H4" t="n">
-        <v>4.594</v>
+        <v>4.5428</v>
       </c>
       <c r="I4" t="n">
         <v>4.6584</v>
@@ -640,7 +640,7 @@
         <v>4.3576</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2781</v>
+        <v>2.2183</v>
       </c>
       <c r="E5" t="n">
         <v>6.6822</v>
@@ -686,7 +686,7 @@
         <v>3.6206</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8215</v>
+        <v>1.768</v>
       </c>
       <c r="E6" t="n">
         <v>5.552</v>
@@ -732,7 +732,7 @@
         <v>3.3196</v>
       </c>
       <c r="D7" t="n">
-        <v>1.635</v>
+        <v>1.5841</v>
       </c>
       <c r="E7" t="n">
         <v>5.0904</v>
@@ -778,7 +778,7 @@
         <v>3.2973</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6213</v>
+        <v>1.5705</v>
       </c>
       <c r="E8" t="n">
         <v>5.0563</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5134</v>
+        <v>4.4784</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9433</v>
+        <v>2.9205</v>
       </c>
       <c r="D9" t="n">
-        <v>1.402</v>
+        <v>1.3403</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5134</v>
+        <v>4.4784</v>
       </c>
       <c r="F9" t="n">
-        <v>4.607</v>
+        <v>4.572</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0936</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9208</v>
+        <v>4.8659</v>
       </c>
       <c r="I9" t="n">
         <v>4.9898</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7887</v>
+        <v>3.7746</v>
       </c>
       <c r="C10" t="n">
-        <v>2.4707</v>
+        <v>2.4615</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1092</v>
+        <v>1.0599</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7887</v>
+        <v>3.7746</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7887</v>
+        <v>3.7746</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7887</v>
+        <v>3.7746</v>
       </c>
       <c r="I10" t="n">
         <v>3.8063</v>
@@ -916,7 +916,7 @@
         <v>2.3744</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0496</v>
+        <v>1.0067</v>
       </c>
       <c r="E11" t="n">
         <v>3.6411</v>
@@ -962,7 +962,7 @@
         <v>2.2678</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9835</v>
+        <v>0.9416</v>
       </c>
       <c r="E12" t="n">
         <v>3.4776</v>
@@ -1008,7 +1008,7 @@
         <v>2.2305</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9604</v>
+        <v>0.9188</v>
       </c>
       <c r="E13" t="n">
         <v>3.4204</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2504</v>
+        <v>3.2297</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1197</v>
+        <v>2.1062</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8917</v>
+        <v>0.8428</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2504</v>
+        <v>3.2297</v>
       </c>
       <c r="F14" t="n">
-        <v>4.2504</v>
+        <v>4.2297</v>
       </c>
       <c r="G14" t="n">
         <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3616</v>
+        <v>4.3292</v>
       </c>
       <c r="I14" t="n">
         <v>4.4023</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1253</v>
+        <v>3.0835</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0381</v>
+        <v>2.0108</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.7846</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1253</v>
+        <v>3.0835</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7571</v>
+        <v>3.7153</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6318</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7571</v>
+        <v>3.7153</v>
       </c>
       <c r="I15" t="n">
         <v>3.8099</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.681</v>
+        <v>2.671</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7483</v>
+        <v>1.7418</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6617</v>
+        <v>0.6202</v>
       </c>
       <c r="E16" t="n">
-        <v>2.681</v>
+        <v>2.671</v>
       </c>
       <c r="F16" t="n">
-        <v>2.681</v>
+        <v>2.671</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.681</v>
+        <v>2.671</v>
       </c>
       <c r="I16" t="n">
         <v>2.6935</v>
@@ -1192,7 +1192,7 @@
         <v>1.6242</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5848</v>
+        <v>0.5483</v>
       </c>
       <c r="E17" t="n">
         <v>2.4906</v>
@@ -1238,7 +1238,7 @@
         <v>1.5737</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5535</v>
+        <v>0.5175</v>
       </c>
       <c r="E18" t="n">
         <v>2.4132</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3482</v>
+        <v>2.3325</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5313</v>
+        <v>1.5211</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5273</v>
+        <v>0.4854</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3482</v>
+        <v>2.3325</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1104</v>
+        <v>2.0947</v>
       </c>
       <c r="G19" t="n">
         <v>0.2378</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1104</v>
+        <v>2.0947</v>
       </c>
       <c r="I19" t="n">
         <v>2.1301</v>
@@ -1330,7 +1330,7 @@
         <v>1.4765</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4933</v>
+        <v>0.4581</v>
       </c>
       <c r="E20" t="n">
         <v>2.2642</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2543</v>
+        <v>2.2459</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4701</v>
+        <v>1.4646</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4893</v>
+        <v>0.4509</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2543</v>
+        <v>2.2459</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2543</v>
+        <v>2.2459</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2543</v>
+        <v>2.2459</v>
       </c>
       <c r="I21" t="n">
         <v>2.2648</v>
@@ -1422,7 +1422,7 @@
         <v>1.3877</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4383</v>
+        <v>0.4039</v>
       </c>
       <c r="E22" t="n">
         <v>2.128</v>
@@ -1468,7 +1468,7 @@
         <v>1.3643</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4238</v>
+        <v>0.3896</v>
       </c>
       <c r="E23" t="n">
         <v>2.0921</v>
@@ -1514,7 +1514,7 @@
         <v>1.3605</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4215</v>
+        <v>0.3873</v>
       </c>
       <c r="E24" t="n">
         <v>2.0863</v>
@@ -1560,7 +1560,7 @@
         <v>1.2949</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3808</v>
+        <v>0.3472</v>
       </c>
       <c r="E25" t="n">
         <v>1.9857</v>
@@ -1606,7 +1606,7 @@
         <v>1.2937</v>
       </c>
       <c r="D26" t="n">
-        <v>0.38</v>
+        <v>0.3464</v>
       </c>
       <c r="E26" t="n">
         <v>1.9838</v>
@@ -1652,7 +1652,7 @@
         <v>1.2485</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3521</v>
+        <v>0.3188</v>
       </c>
       <c r="E27" t="n">
         <v>1.9145</v>
@@ -1698,7 +1698,7 @@
         <v>1.0956</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2573</v>
+        <v>0.2254</v>
       </c>
       <c r="E28" t="n">
         <v>1.68</v>
@@ -1744,7 +1744,7 @@
         <v>1.088</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2526</v>
+        <v>0.2208</v>
       </c>
       <c r="E29" t="n">
         <v>1.6684</v>
@@ -1790,7 +1790,7 @@
         <v>1.0483</v>
       </c>
       <c r="D30" t="n">
-        <v>0.228</v>
+        <v>0.1965</v>
       </c>
       <c r="E30" t="n">
         <v>1.6075</v>
@@ -1836,7 +1836,7 @@
         <v>1.045</v>
       </c>
       <c r="D31" t="n">
-        <v>0.226</v>
+        <v>0.1945</v>
       </c>
       <c r="E31" t="n">
         <v>1.6024</v>
@@ -1882,7 +1882,7 @@
         <v>1.0305</v>
       </c>
       <c r="D32" t="n">
-        <v>0.217</v>
+        <v>0.1857</v>
       </c>
       <c r="E32" t="n">
         <v>1.5803</v>
@@ -1928,7 +1928,7 @@
         <v>0.9815</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1867</v>
+        <v>0.1557</v>
       </c>
       <c r="E33" t="n">
         <v>1.5051</v>
@@ -1974,7 +1974,7 @@
         <v>0.9246</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1514</v>
+        <v>0.121</v>
       </c>
       <c r="E34" t="n">
         <v>1.4179</v>
@@ -2020,7 +2020,7 @@
         <v>0.7959000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0717</v>
+        <v>0.0423</v>
       </c>
       <c r="E35" t="n">
         <v>1.2205</v>
@@ -2066,7 +2066,7 @@
         <v>0.7607</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0499</v>
+        <v>0.0208</v>
       </c>
       <c r="E36" t="n">
         <v>1.1665</v>
@@ -2112,7 +2112,7 @@
         <v>0.6896</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0058</v>
+        <v>-0.0226</v>
       </c>
       <c r="E37" t="n">
         <v>1.0575</v>
@@ -2158,7 +2158,7 @@
         <v>0.6614</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0116</v>
+        <v>-0.0398</v>
       </c>
       <c r="E38" t="n">
         <v>1.0143</v>
@@ -2204,7 +2204,7 @@
         <v>0.6207</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0369</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="E39" t="n">
         <v>0.9518</v>
@@ -2250,7 +2250,7 @@
         <v>0.5845</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0593</v>
+        <v>-0.0868</v>
       </c>
       <c r="E40" t="n">
         <v>0.8963</v>
@@ -2296,7 +2296,7 @@
         <v>0.5104</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1052</v>
+        <v>-0.1321</v>
       </c>
       <c r="E41" t="n">
         <v>0.7826</v>
@@ -2342,7 +2342,7 @@
         <v>0.2652</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2571</v>
+        <v>-0.2819</v>
       </c>
       <c r="E42" t="n">
         <v>0.4067</v>
@@ -2388,7 +2388,7 @@
         <v>0.2357</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2754</v>
+        <v>-0.2999</v>
       </c>
       <c r="E43" t="n">
         <v>0.3614</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3595</v>
+        <v>0.3494</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2344</v>
+        <v>0.2279</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2761</v>
+        <v>-0.3047</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3595</v>
+        <v>0.3494</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3595</v>
+        <v>1.3494</v>
       </c>
       <c r="G44" t="n">
         <v>-1</v>
       </c>
       <c r="H44" t="n">
-        <v>1.3595</v>
+        <v>1.3494</v>
       </c>
       <c r="I44" t="n">
         <v>1.3722</v>
@@ -2480,7 +2480,7 @@
         <v>0.2178</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2864</v>
+        <v>-0.3108</v>
       </c>
       <c r="E45" t="n">
         <v>0.334</v>
@@ -2526,7 +2526,7 @@
         <v>0.1601</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3222</v>
+        <v>-0.3461</v>
       </c>
       <c r="E46" t="n">
         <v>0.2455</v>
@@ -2572,7 +2572,7 @@
         <v>0.1047</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3565</v>
+        <v>-0.3799</v>
       </c>
       <c r="E47" t="n">
         <v>0.1606</v>
@@ -2618,7 +2618,7 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.36</v>
+        <v>-0.3834</v>
       </c>
       <c r="E48" t="n">
         <v>0.1519</v>
@@ -2664,7 +2664,7 @@
         <v>0.0636</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.382</v>
+        <v>-0.4051</v>
       </c>
       <c r="E49" t="n">
         <v>0.0975</v>
@@ -2710,7 +2710,7 @@
         <v>0.0237</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4067</v>
+        <v>-0.4294</v>
       </c>
       <c r="E50" t="n">
         <v>0.0364</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1012</v>
+        <v>-0.1009</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.066</v>
+        <v>-0.0658</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4622</v>
+        <v>-0.4841</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1012</v>
+        <v>-0.1009</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1012</v>
+        <v>-0.1009</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1012</v>
+        <v>-0.1009</v>
       </c>
       <c r="I51" t="n">
         <v>-0.1017</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1006</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4837</v>
+        <v>-0.5054</v>
       </c>
       <c r="E52" t="n">
         <v>-0.1543</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1235</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4979</v>
+        <v>-0.5194</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1894</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2324</v>
+        <v>-0.2315</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1516</v>
+        <v>-0.151</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5152</v>
+        <v>-0.5361</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2324</v>
+        <v>-0.2315</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2324</v>
+        <v>-0.2315</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2324</v>
+        <v>-0.2315</v>
       </c>
       <c r="I54" t="n">
         <v>-0.2335</v>
@@ -2940,7 +2940,7 @@
         <v>-0.1617</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5215</v>
+        <v>-0.5427</v>
       </c>
       <c r="E55" t="n">
         <v>-0.248</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1619</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2483</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1865</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5369</v>
+        <v>-0.5579</v>
       </c>
       <c r="E57" t="n">
         <v>-0.286</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2377</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5686</v>
+        <v>-0.5891</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3645</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2936</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6032</v>
+        <v>-0.6233</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4502</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3461</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6358</v>
+        <v>-0.6553</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5306999999999999</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3474</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.6561</v>
       </c>
       <c r="E61" t="n">
         <v>-0.5327</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3573</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6427</v>
+        <v>-0.6622</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5479000000000001</v>
@@ -3308,7 +3308,7 @@
         <v>-0.417</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6797</v>
+        <v>-0.6986</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6394</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4787</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7179</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7341</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5172</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7418</v>
+        <v>-0.7599</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7931</v>
@@ -3446,7 +3446,7 @@
         <v>-0.6183</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8044</v>
+        <v>-0.8217</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9482</v>
@@ -3492,7 +3492,7 @@
         <v>-0.6358</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8152</v>
+        <v>-0.8324</v>
       </c>
       <c r="E67" t="n">
         <v>-0.975</v>
@@ -3538,7 +3538,7 @@
         <v>-0.8003</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9172</v>
+        <v>-0.9329</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2273</v>
@@ -3584,7 +3584,7 @@
         <v>-0.8149999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9263</v>
+        <v>-0.9418</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2498</v>
@@ -3630,7 +3630,7 @@
         <v>-0.8159999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.9424</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2513</v>
@@ -3676,7 +3676,7 @@
         <v>-0.8583</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.953</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3161</v>
@@ -3722,7 +3722,7 @@
         <v>-1.0206</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0536</v>
+        <v>-1.0674</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5651</v>
@@ -3758,93 +3758,93 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.6013</v>
+        <v>-1.5976</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.0442</v>
+        <v>-1.0418</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0683</v>
+        <v>-1.0804</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.6013</v>
+        <v>-1.5976</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.6013</v>
+        <v>-0.7217</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-0.8759</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.6013</v>
+        <v>-0.7217</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.6013</v>
+        <v>-0.7339</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>-0.8759</v>
       </c>
       <c r="K73" t="n">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.6013</v>
+        <v>-1.6098</v>
       </c>
       <c r="N73" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.603</v>
+        <v>-1.6013</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.0454</v>
+        <v>-1.0442</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0689</v>
+        <v>-1.0819</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.603</v>
+        <v>-1.6013</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7271</v>
+        <v>-1.6013</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.8759</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7271</v>
+        <v>-1.6013</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7339</v>
+        <v>-1.6013</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.8759</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="L74" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.6098</v>
+        <v>-1.6013</v>
       </c>
       <c r="N74" t="n">
-        <v>215</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75">
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.6105</v>
+        <v>-1.606</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.0502</v>
+        <v>-1.0473</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.072</v>
+        <v>-1.0837</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.6105</v>
+        <v>-1.606</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.6105</v>
+        <v>-0.606</v>
       </c>
       <c r="G75" t="n">
         <v>-1</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.6105</v>
+        <v>-0.606</v>
       </c>
       <c r="I75" t="n">
         <v>-0.6162</v>
@@ -3906,7 +3906,7 @@
         <v>-1.0791</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0898</v>
+        <v>-1.1031</v>
       </c>
       <c r="E76" t="n">
         <v>-1.6547</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1432</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1296</v>
+        <v>-1.1423</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7531</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1905</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1589</v>
+        <v>-1.1712</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8256</v>
@@ -4044,7 +4044,7 @@
         <v>-1.3042</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E79" t="n">
         <v>-2</v>
@@ -4090,7 +4090,7 @@
         <v>-1.3042</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E80" t="n">
         <v>-2</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.8647</v>
+        <v>-3.8356</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.5203</v>
+        <v>-2.5013</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.9826</v>
+        <v>-1.972</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.8647</v>
+        <v>-3.8356</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.6148</v>
+        <v>-2.5857</v>
       </c>
       <c r="G81" t="n">
         <v>-1.2499</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.6148</v>
+        <v>-2.5857</v>
       </c>
       <c r="I81" t="n">
         <v>-2.6515</v>

--- a/database/event/7904/event_7904_evp_summary.xlsx
+++ b/database/event/7904/event_7904_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.6555</v>
+        <v>11.91</v>
       </c>
       <c r="C2" t="n">
-        <v>7.6008</v>
+        <v>7.7668</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6816</v>
+        <v>4.7061</v>
       </c>
       <c r="E2" t="n">
-        <v>11.6555</v>
+        <v>11.91</v>
       </c>
       <c r="F2" t="n">
         <v>4.5807</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0748</v>
+        <v>7.0732</v>
       </c>
       <c r="H2" t="n">
-        <v>13.2493</v>
+        <v>13.2293</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1545</v>
+        <v>7.1437</v>
       </c>
       <c r="J2" t="n">
-        <v>7.1824</v>
+        <v>7.1661</v>
       </c>
       <c r="K2" t="n">
         <v>121</v>
@@ -529,7 +529,7 @@
         <v>161</v>
       </c>
       <c r="M2" t="n">
-        <v>14.3369</v>
+        <v>14.3098</v>
       </c>
       <c r="N2" t="n">
         <v>282</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.2143</v>
+        <v>8.671200000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>5.3567</v>
+        <v>5.6547</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1151</v>
+        <v>3.2594</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2143</v>
+        <v>8.671200000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2512</v>
+        <v>4.243</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9631</v>
+        <v>3.9627</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5796</v>
+        <v>6.5617</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1015</v>
+        <v>7.0821</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9631</v>
+        <v>3.9627</v>
       </c>
       <c r="K3" t="n">
         <v>217</v>
@@ -575,7 +575,7 @@
         <v>99</v>
       </c>
       <c r="M3" t="n">
-        <v>11.0646</v>
+        <v>11.0448</v>
       </c>
       <c r="N3" t="n">
         <v>316</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0409</v>
+        <v>6.2096</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9394</v>
+        <v>4.0494</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1257</v>
+        <v>2.1599</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0409</v>
+        <v>6.2096</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8519</v>
+        <v>3.4626</v>
       </c>
       <c r="G4" t="n">
-        <v>2.189</v>
+        <v>2.5008</v>
       </c>
       <c r="H4" t="n">
-        <v>7.8146</v>
+        <v>4.8536</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2198</v>
+        <v>5.2386</v>
       </c>
       <c r="J4" t="n">
-        <v>2.189</v>
+        <v>2.5008</v>
       </c>
       <c r="K4" t="n">
-        <v>121</v>
+        <v>217</v>
       </c>
       <c r="L4" t="n">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="M4" t="n">
-        <v>6.4088</v>
+        <v>7.7394</v>
       </c>
       <c r="N4" t="n">
-        <v>282</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9636</v>
+        <v>6.0676</v>
       </c>
       <c r="C5" t="n">
-        <v>3.889</v>
+        <v>3.9568</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0905</v>
+        <v>2.0964</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9636</v>
+        <v>6.0676</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4623</v>
+        <v>3.8523</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5013</v>
+        <v>2.1897</v>
       </c>
       <c r="H5" t="n">
-        <v>4.853</v>
+        <v>7.816</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2379</v>
+        <v>4.2206</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5013</v>
+        <v>2.1897</v>
       </c>
       <c r="K5" t="n">
-        <v>217</v>
+        <v>121</v>
       </c>
       <c r="L5" t="n">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="M5" t="n">
-        <v>7.7392</v>
+        <v>6.4103</v>
       </c>
       <c r="N5" t="n">
-        <v>316</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4909</v>
+        <v>5.4734</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5807</v>
+        <v>3.5693</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8754</v>
+        <v>1.831</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4909</v>
+        <v>5.4734</v>
       </c>
       <c r="F6" t="n">
-        <v>3.234</v>
+        <v>3.2192</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2569</v>
+        <v>2.2582</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7758</v>
+        <v>5.7271</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1189</v>
+        <v>3.0926</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2569</v>
+        <v>2.2582</v>
       </c>
       <c r="K6" t="n">
         <v>121</v>
@@ -713,7 +713,7 @@
         <v>161</v>
       </c>
       <c r="M6" t="n">
-        <v>5.3758</v>
+        <v>5.3508</v>
       </c>
       <c r="N6" t="n">
         <v>282</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9117</v>
+        <v>4.9302</v>
       </c>
       <c r="C7" t="n">
-        <v>3.203</v>
+        <v>3.2151</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6117</v>
+        <v>1.5884</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9117</v>
+        <v>4.9302</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4028</v>
+        <v>3.6536</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5089</v>
+        <v>1.011</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5341</v>
+        <v>7.1603</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5341</v>
+        <v>3.8665</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5089</v>
+        <v>1.011</v>
       </c>
       <c r="K7" t="n">
-        <v>187</v>
+        <v>126</v>
       </c>
       <c r="L7" t="n">
-        <v>185</v>
+        <v>47</v>
       </c>
       <c r="M7" t="n">
-        <v>5.043</v>
+        <v>4.8775</v>
       </c>
       <c r="N7" t="n">
-        <v>372</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6648</v>
+        <v>4.9108</v>
       </c>
       <c r="C8" t="n">
-        <v>3.042</v>
+        <v>3.2024</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4993</v>
+        <v>1.5797</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6648</v>
+        <v>4.9108</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6538</v>
+        <v>2.4028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.011</v>
+        <v>2.5301</v>
       </c>
       <c r="H8" t="n">
-        <v>7.1612</v>
+        <v>2.534</v>
       </c>
       <c r="I8" t="n">
-        <v>3.867</v>
+        <v>2.534</v>
       </c>
       <c r="J8" t="n">
-        <v>1.011</v>
+        <v>2.5301</v>
       </c>
       <c r="K8" t="n">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="L8" t="n">
-        <v>47</v>
+        <v>185</v>
       </c>
       <c r="M8" t="n">
-        <v>4.878</v>
+        <v>5.0641</v>
       </c>
       <c r="N8" t="n">
-        <v>173</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7897</v>
+        <v>3.8634</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4713</v>
+        <v>2.5194</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1009</v>
+        <v>1.1119</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7897</v>
+        <v>3.8634</v>
       </c>
       <c r="F9" t="n">
         <v>3.6207</v>
       </c>
       <c r="G9" t="n">
-        <v>0.169</v>
+        <v>0.1688</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1996</v>
+        <v>5.1997</v>
       </c>
       <c r="I9" t="n">
-        <v>5.612</v>
+        <v>5.6121</v>
       </c>
       <c r="J9" t="n">
-        <v>0.169</v>
+        <v>0.1688</v>
       </c>
       <c r="K9" t="n">
         <v>217</v>
@@ -851,7 +851,7 @@
         <v>99</v>
       </c>
       <c r="M9" t="n">
-        <v>5.781</v>
+        <v>5.7809</v>
       </c>
       <c r="N9" t="n">
         <v>316</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6284</v>
+        <v>3.7326</v>
       </c>
       <c r="C10" t="n">
-        <v>2.3662</v>
+        <v>2.4341</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0275</v>
+        <v>1.0535</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6284</v>
+        <v>3.7326</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9673</v>
+        <v>1.9674</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6611</v>
+        <v>1.6604</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9673</v>
+        <v>1.9674</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9673</v>
+        <v>1.9674</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6611</v>
+        <v>1.6604</v>
       </c>
       <c r="K10" t="n">
         <v>187</v>
@@ -897,7 +897,7 @@
         <v>185</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6284</v>
+        <v>3.6278</v>
       </c>
       <c r="N10" t="n">
         <v>372</v>
@@ -906,47 +906,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2953</v>
+        <v>3.4045</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1489</v>
+        <v>2.2201</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8759</v>
+        <v>0.9069</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2953</v>
+        <v>3.4045</v>
       </c>
       <c r="F11" t="n">
-        <v>3.569</v>
+        <v>2.8875</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2737</v>
+        <v>0.192</v>
       </c>
       <c r="H11" t="n">
-        <v>5.0866</v>
+        <v>3.5948</v>
       </c>
       <c r="I11" t="n">
-        <v>5.49</v>
+        <v>3.7825</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2737</v>
+        <v>0.192</v>
       </c>
       <c r="K11" t="n">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="L11" t="n">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2163</v>
+        <v>3.9745</v>
       </c>
       <c r="N11" t="n">
-        <v>316</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2911</v>
+        <v>3.4008</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1462</v>
+        <v>2.2177</v>
       </c>
       <c r="D12" t="n">
-        <v>0.874</v>
+        <v>0.9052</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2911</v>
+        <v>3.4008</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2911</v>
+        <v>3.2913</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4783</v>
+        <v>4.4786</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4783</v>
+        <v>4.4786</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4783</v>
+        <v>4.4786</v>
       </c>
       <c r="N12" t="n">
         <v>252</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1866</v>
+        <v>3.207</v>
       </c>
       <c r="C13" t="n">
-        <v>2.078</v>
+        <v>2.0914</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8264</v>
+        <v>0.8187</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1866</v>
+        <v>3.207</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1371</v>
+        <v>3.5691</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0495</v>
+        <v>-0.2646</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4564</v>
+        <v>5.0866</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9464</v>
+        <v>5.4901</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0495</v>
+        <v>-0.2646</v>
       </c>
       <c r="K13" t="n">
-        <v>126</v>
+        <v>217</v>
       </c>
       <c r="L13" t="n">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9959</v>
+        <v>5.2255</v>
       </c>
       <c r="N13" t="n">
-        <v>173</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1529</v>
+        <v>3.1967</v>
       </c>
       <c r="C14" t="n">
-        <v>2.0561</v>
+        <v>2.0846</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8111</v>
+        <v>0.8141</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1529</v>
+        <v>3.1967</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2594</v>
+        <v>2.2753</v>
       </c>
       <c r="G14" t="n">
         <v>0.8935</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5604</v>
+        <v>2.613</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3826</v>
+        <v>1.411</v>
       </c>
       <c r="J14" t="n">
         <v>0.8935</v>
@@ -1081,7 +1081,7 @@
         <v>47</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2761</v>
+        <v>2.3045</v>
       </c>
       <c r="N14" t="n">
         <v>173</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0792</v>
+        <v>3.1895</v>
       </c>
       <c r="C15" t="n">
-        <v>2.008</v>
+        <v>2.0799</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7775</v>
+        <v>0.8109</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0792</v>
+        <v>3.1895</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8872</v>
+        <v>3.1446</v>
       </c>
       <c r="G15" t="n">
-        <v>0.192</v>
+        <v>0.0495</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5943</v>
+        <v>5.481</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7819</v>
+        <v>2.9597</v>
       </c>
       <c r="J15" t="n">
-        <v>0.192</v>
+        <v>0.0495</v>
       </c>
       <c r="K15" t="n">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="L15" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9739</v>
+        <v>3.0092</v>
       </c>
       <c r="N15" t="n">
-        <v>215</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9694</v>
+        <v>3.0564</v>
       </c>
       <c r="C16" t="n">
-        <v>1.9364</v>
+        <v>1.9931</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7275</v>
+        <v>0.7514</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9694</v>
+        <v>3.0564</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9694</v>
+        <v>2.9679</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7741</v>
+        <v>3.7708</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8714</v>
+        <v>3.868</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8714</v>
+        <v>3.868</v>
       </c>
       <c r="N16" t="n">
         <v>209</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8698</v>
+        <v>3.0128</v>
       </c>
       <c r="C17" t="n">
-        <v>1.8715</v>
+        <v>1.9647</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6822</v>
+        <v>0.7319</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8698</v>
+        <v>3.0128</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8698</v>
+        <v>2.87</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5561</v>
+        <v>3.5567</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5561</v>
+        <v>3.5567</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5561</v>
+        <v>3.5567</v>
       </c>
       <c r="N17" t="n">
         <v>140</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.7786</v>
+        <v>2.7662</v>
       </c>
       <c r="C18" t="n">
-        <v>1.812</v>
+        <v>1.8039</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6407</v>
+        <v>0.6218</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7786</v>
+        <v>2.7662</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7786</v>
+        <v>2.773</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3565</v>
+        <v>3.3442</v>
       </c>
       <c r="I18" t="n">
-        <v>3.443</v>
+        <v>3.4304</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.443</v>
+        <v>3.4304</v>
       </c>
       <c r="N18" t="n">
         <v>209</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.7667</v>
+        <v>2.7166</v>
       </c>
       <c r="C19" t="n">
-        <v>1.8042</v>
+        <v>1.7716</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6353</v>
+        <v>0.5996</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7667</v>
+        <v>2.7166</v>
       </c>
       <c r="F19" t="n">
-        <v>3.5481</v>
+        <v>3.5485</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7814</v>
       </c>
       <c r="H19" t="n">
-        <v>5.0408</v>
+        <v>5.0416</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3039</v>
+        <v>5.3048</v>
       </c>
       <c r="J19" t="n">
         <v>-0.7814</v>
@@ -1311,7 +1311,7 @@
         <v>37</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5225</v>
+        <v>4.523400000000001</v>
       </c>
       <c r="N19" t="n">
         <v>215</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.5532</v>
+        <v>2.6929</v>
       </c>
       <c r="C20" t="n">
-        <v>1.665</v>
+        <v>1.7561</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5381</v>
+        <v>0.589</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5532</v>
+        <v>2.6929</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5532</v>
+        <v>2.5488</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8633</v>
+        <v>2.8537</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8633</v>
+        <v>2.8537</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8633</v>
+        <v>2.8537</v>
       </c>
       <c r="N20" t="n">
         <v>252</v>
@@ -1366,461 +1366,461 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5306</v>
+        <v>2.6873</v>
       </c>
       <c r="C21" t="n">
-        <v>1.6503</v>
+        <v>1.7524</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5278</v>
+        <v>0.5865</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5306</v>
+        <v>2.6873</v>
       </c>
       <c r="F21" t="n">
-        <v>3.0467</v>
+        <v>2.4673</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5161</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5.158</v>
+        <v>2.6752</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7853</v>
+        <v>2.6752</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5161</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="L21" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.2692</v>
+        <v>2.6752</v>
       </c>
       <c r="N21" t="n">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.4639</v>
+        <v>2.5286</v>
       </c>
       <c r="C22" t="n">
-        <v>1.6068</v>
+        <v>1.649</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4974</v>
+        <v>0.5157</v>
       </c>
       <c r="E22" t="n">
-        <v>2.4639</v>
+        <v>2.5286</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4639</v>
+        <v>2.2947</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6678</v>
+        <v>2.2975</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6678</v>
+        <v>2.2975</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.6678</v>
+        <v>2.2975</v>
       </c>
       <c r="N22" t="n">
-        <v>152</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.361</v>
+        <v>2.5268</v>
       </c>
       <c r="C23" t="n">
-        <v>1.5397</v>
+        <v>1.6478</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4506</v>
+        <v>0.5148</v>
       </c>
       <c r="E23" t="n">
-        <v>2.361</v>
+        <v>2.5268</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0241</v>
+        <v>2.2654</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3369</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0241</v>
+        <v>2.2654</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0241</v>
+        <v>2.3238</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3369</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>152</v>
+        <v>209</v>
       </c>
       <c r="L23" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.361</v>
+        <v>2.3238</v>
       </c>
       <c r="N23" t="n">
-        <v>191</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3046</v>
+        <v>2.4974</v>
       </c>
       <c r="C24" t="n">
-        <v>1.5029</v>
+        <v>1.6286</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4249</v>
+        <v>0.5017</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3046</v>
+        <v>2.4974</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3046</v>
+        <v>2.1764</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3191</v>
+        <v>2.1764</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3191</v>
+        <v>2.1764</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.3191</v>
+        <v>2.1764</v>
       </c>
       <c r="N24" t="n">
-        <v>196</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.2467</v>
+        <v>2.4262</v>
       </c>
       <c r="C25" t="n">
-        <v>1.4651</v>
+        <v>1.5822</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3985</v>
+        <v>0.4699</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2467</v>
+        <v>2.4262</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1071</v>
+        <v>3.0465</v>
       </c>
       <c r="G25" t="n">
-        <v>1.1396</v>
+        <v>-0.5161</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1071</v>
+        <v>5.1575</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1071</v>
+        <v>2.785</v>
       </c>
       <c r="J25" t="n">
-        <v>1.1396</v>
+        <v>-0.5161</v>
       </c>
       <c r="K25" t="n">
-        <v>187</v>
+        <v>126</v>
       </c>
       <c r="L25" t="n">
-        <v>185</v>
+        <v>47</v>
       </c>
       <c r="M25" t="n">
-        <v>2.2467</v>
+        <v>2.2689</v>
       </c>
       <c r="N25" t="n">
-        <v>372</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>nin9</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.2348</v>
+        <v>2.4172</v>
       </c>
       <c r="C26" t="n">
-        <v>1.4574</v>
+        <v>1.5763</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3931</v>
+        <v>0.4659</v>
       </c>
       <c r="E26" t="n">
-        <v>2.2348</v>
+        <v>2.4172</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2348</v>
+        <v>1.9793</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2348</v>
+        <v>1.9793</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2924</v>
+        <v>1.9793</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>209</v>
+        <v>86</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.2924</v>
+        <v>1.9793</v>
       </c>
       <c r="N26" t="n">
-        <v>209</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2213</v>
+        <v>2.3747</v>
       </c>
       <c r="C27" t="n">
-        <v>1.4486</v>
+        <v>1.5486</v>
       </c>
       <c r="D27" t="n">
-        <v>0.387</v>
+        <v>0.4469</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2213</v>
+        <v>2.3747</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4735</v>
+        <v>2.0236</v>
       </c>
       <c r="G27" t="n">
-        <v>1.7478</v>
+        <v>0.3364</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4735</v>
+        <v>2.0236</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4735</v>
+        <v>2.0236</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7478</v>
+        <v>0.3364</v>
       </c>
       <c r="K27" t="n">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="L27" t="n">
-        <v>185</v>
+        <v>39</v>
       </c>
       <c r="M27" t="n">
-        <v>2.2213</v>
+        <v>2.36</v>
       </c>
       <c r="N27" t="n">
-        <v>372</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.2207</v>
+        <v>2.3345</v>
       </c>
       <c r="C28" t="n">
-        <v>1.4482</v>
+        <v>1.5224</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3867</v>
+        <v>0.4289</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2207</v>
+        <v>2.3345</v>
       </c>
       <c r="F28" t="n">
-        <v>2.2207</v>
+        <v>1.089</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.1394</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2207</v>
+        <v>1.089</v>
       </c>
       <c r="I28" t="n">
-        <v>2.2207</v>
+        <v>1.089</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1.1394</v>
       </c>
       <c r="K28" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="M28" t="n">
-        <v>2.2207</v>
+        <v>2.2284</v>
       </c>
       <c r="N28" t="n">
-        <v>196</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.2035</v>
+        <v>2.3254</v>
       </c>
       <c r="C29" t="n">
-        <v>1.4369</v>
+        <v>1.5164</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3789</v>
+        <v>0.4249</v>
       </c>
       <c r="E29" t="n">
-        <v>2.2035</v>
+        <v>2.3254</v>
       </c>
       <c r="F29" t="n">
-        <v>3.5551</v>
+        <v>0.4739</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.3516</v>
+        <v>1.7476</v>
       </c>
       <c r="H29" t="n">
-        <v>6.8355</v>
+        <v>0.4739</v>
       </c>
       <c r="I29" t="n">
-        <v>3.6911</v>
+        <v>0.4739</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.3516</v>
+        <v>1.7476</v>
       </c>
       <c r="K29" t="n">
-        <v>121</v>
+        <v>187</v>
       </c>
       <c r="L29" t="n">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="M29" t="n">
-        <v>2.3395</v>
+        <v>2.2215</v>
       </c>
       <c r="N29" t="n">
-        <v>282</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.1764</v>
+        <v>2.3129</v>
       </c>
       <c r="C30" t="n">
-        <v>1.4193</v>
+        <v>1.5083</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3665</v>
+        <v>0.4193</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1764</v>
+        <v>2.3129</v>
       </c>
       <c r="F30" t="n">
-        <v>2.1764</v>
+        <v>2.2226</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.1764</v>
+        <v>2.2226</v>
       </c>
       <c r="I30" t="n">
-        <v>2.1764</v>
+        <v>2.2226</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.1764</v>
+        <v>2.2226</v>
       </c>
       <c r="N30" t="n">
-        <v>128</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.0856</v>
+        <v>2.0543</v>
       </c>
       <c r="C31" t="n">
-        <v>1.3601</v>
+        <v>1.3397</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3252</v>
+        <v>0.3038</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0856</v>
+        <v>2.0543</v>
       </c>
       <c r="F31" t="n">
-        <v>2.7504</v>
+        <v>2.7501</v>
       </c>
       <c r="G31" t="n">
         <v>-0.6647999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>4.1802</v>
+        <v>4.1795</v>
       </c>
       <c r="I31" t="n">
-        <v>2.2573</v>
+        <v>2.2569</v>
       </c>
       <c r="J31" t="n">
         <v>-0.6647999999999999</v>
@@ -1863,7 +1863,7 @@
         <v>47</v>
       </c>
       <c r="M31" t="n">
-        <v>1.5925</v>
+        <v>1.5921</v>
       </c>
       <c r="N31" t="n">
         <v>173</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nin9</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.9807</v>
+        <v>1.9988</v>
       </c>
       <c r="C32" t="n">
-        <v>1.2917</v>
+        <v>1.3035</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2775</v>
+        <v>0.279</v>
       </c>
       <c r="E32" t="n">
-        <v>1.9807</v>
+        <v>1.9988</v>
       </c>
       <c r="F32" t="n">
-        <v>1.9807</v>
+        <v>3.5555</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-1.3508</v>
       </c>
       <c r="H32" t="n">
-        <v>1.9807</v>
+        <v>6.8366</v>
       </c>
       <c r="I32" t="n">
-        <v>1.9807</v>
+        <v>3.6917</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-1.3508</v>
       </c>
       <c r="K32" t="n">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M32" t="n">
-        <v>1.9807</v>
+        <v>2.3409</v>
       </c>
       <c r="N32" t="n">
-        <v>86</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33">
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.9605</v>
+        <v>1.9393</v>
       </c>
       <c r="C33" t="n">
-        <v>1.2785</v>
+        <v>1.2647</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2683</v>
+        <v>0.2524</v>
       </c>
       <c r="E33" t="n">
-        <v>1.9605</v>
+        <v>1.9393</v>
       </c>
       <c r="F33" t="n">
         <v>1.9605</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.7522</v>
+        <v>1.7592</v>
       </c>
       <c r="C34" t="n">
-        <v>1.1426</v>
+        <v>1.1472</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1734</v>
+        <v>0.172</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7522</v>
+        <v>1.7592</v>
       </c>
       <c r="F34" t="n">
-        <v>1.7522</v>
+        <v>1.9283</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.3202</v>
       </c>
       <c r="H34" t="n">
-        <v>1.7522</v>
+        <v>1.9283</v>
       </c>
       <c r="I34" t="n">
-        <v>1.7522</v>
+        <v>1.9283</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.3202</v>
       </c>
       <c r="K34" t="n">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M34" t="n">
-        <v>1.7522</v>
+        <v>1.6081</v>
       </c>
       <c r="N34" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.6087</v>
+        <v>1.7092</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0491</v>
+        <v>1.1146</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1081</v>
+        <v>0.1496</v>
       </c>
       <c r="E35" t="n">
-        <v>1.6087</v>
+        <v>1.7092</v>
       </c>
       <c r="F35" t="n">
-        <v>1.9287</v>
+        <v>1.7512</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.9287</v>
+        <v>1.7512</v>
       </c>
       <c r="I35" t="n">
-        <v>1.9287</v>
+        <v>1.7512</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="L35" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.6087</v>
+        <v>1.7512</v>
       </c>
       <c r="N35" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4546</v>
+        <v>1.5745</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9486</v>
+        <v>1.0268</v>
       </c>
       <c r="D36" t="n">
-        <v>0.038</v>
+        <v>0.0895</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4546</v>
+        <v>1.5745</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4546</v>
+        <v>1.4532</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.4546</v>
+        <v>1.4532</v>
       </c>
       <c r="I36" t="n">
-        <v>1.4546</v>
+        <v>1.4532</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4546</v>
+        <v>1.4532</v>
       </c>
       <c r="N36" t="n">
         <v>152</v>
@@ -2102,277 +2102,277 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.4189</v>
+        <v>1.4309</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9253</v>
+        <v>0.9331</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0217</v>
+        <v>0.0253</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4189</v>
+        <v>1.4309</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4189</v>
+        <v>2.2285</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.9187</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4189</v>
+        <v>2.2285</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4189</v>
+        <v>2.3448</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.9187</v>
       </c>
       <c r="K37" t="n">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4189</v>
+        <v>1.4261</v>
       </c>
       <c r="N37" t="n">
-        <v>152</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3982</v>
+        <v>1.3853</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9034</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0123</v>
+        <v>0.005</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3982</v>
+        <v>1.3853</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3982</v>
+        <v>1.3901</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3982</v>
+        <v>1.3901</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3982</v>
+        <v>1.3901</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>252</v>
+        <v>128</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3982</v>
+        <v>1.3901</v>
       </c>
       <c r="N38" t="n">
-        <v>252</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.3923</v>
+        <v>1.3485</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9079</v>
+        <v>0.8794</v>
       </c>
       <c r="D39" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0115</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3923</v>
+        <v>1.3485</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3923</v>
+        <v>1.3495</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.3923</v>
+        <v>1.3495</v>
       </c>
       <c r="I39" t="n">
-        <v>1.3923</v>
+        <v>1.3495</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>196</v>
+        <v>140</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3923</v>
+        <v>1.3495</v>
       </c>
       <c r="N39" t="n">
-        <v>196</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.3901</v>
+        <v>1.32</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9065</v>
+        <v>0.8608</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0086</v>
+        <v>-0.0242</v>
       </c>
       <c r="E40" t="n">
-        <v>1.3901</v>
+        <v>1.32</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3901</v>
+        <v>1.4469</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.3901</v>
+        <v>1.4469</v>
       </c>
       <c r="I40" t="n">
-        <v>1.3901</v>
+        <v>1.4469</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.3901</v>
+        <v>1.4469</v>
       </c>
       <c r="N40" t="n">
-        <v>128</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.3531</v>
+        <v>1.3148</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8824</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0265</v>
       </c>
       <c r="E41" t="n">
-        <v>1.3531</v>
+        <v>1.3148</v>
       </c>
       <c r="F41" t="n">
-        <v>2.2718</v>
+        <v>1.4084</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9187</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.2718</v>
+        <v>1.4084</v>
       </c>
       <c r="I41" t="n">
-        <v>2.3904</v>
+        <v>1.4084</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9187</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="L41" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.4717</v>
+        <v>1.4084</v>
       </c>
       <c r="N41" t="n">
-        <v>215</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.3492</v>
+        <v>1.2914</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8798</v>
+        <v>0.8421</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.01</v>
+        <v>-0.037</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3492</v>
+        <v>1.2914</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3492</v>
+        <v>1.3862</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.3492</v>
+        <v>1.3862</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3492</v>
+        <v>1.3862</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>140</v>
+        <v>252</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.3492</v>
+        <v>1.3862</v>
       </c>
       <c r="N42" t="n">
-        <v>140</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.2349</v>
+        <v>1.0817</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8053</v>
+        <v>0.7054</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0621</v>
+        <v>-0.1306</v>
       </c>
       <c r="E43" t="n">
-        <v>1.2349</v>
+        <v>1.0817</v>
       </c>
       <c r="F43" t="n">
-        <v>1.2349</v>
+        <v>1.2346</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.2349</v>
+        <v>1.2346</v>
       </c>
       <c r="I43" t="n">
-        <v>1.2667</v>
+        <v>1.2664</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.2667</v>
+        <v>1.2664</v>
       </c>
       <c r="N43" t="n">
         <v>209</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9776</v>
+        <v>1.0287</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6375</v>
+        <v>0.6708</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1792</v>
+        <v>-0.1543</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9776</v>
+        <v>1.0287</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9776</v>
+        <v>0.9553</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9776</v>
+        <v>0.9553</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9776</v>
+        <v>0.9553</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.9776</v>
+        <v>0.9553</v>
       </c>
       <c r="N44" t="n">
         <v>140</v>
@@ -2470,47 +2470,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6804</v>
+        <v>0.6528</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4437</v>
+        <v>0.4257</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3145</v>
+        <v>-0.3222</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6804</v>
+        <v>0.6528</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6804</v>
+        <v>0.627</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6804</v>
+        <v>0.627</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6804</v>
+        <v>0.627</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>252</v>
+        <v>75</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6804</v>
+        <v>0.627</v>
       </c>
       <c r="N45" t="n">
-        <v>252</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46">
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6652</v>
+        <v>0.5607</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4338</v>
+        <v>0.3656</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3214</v>
+        <v>-0.3634</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6652</v>
+        <v>0.5607</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6652</v>
+        <v>0.6655</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6652</v>
+        <v>0.6655</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6652</v>
+        <v>0.6655</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6652</v>
+        <v>0.6655</v>
       </c>
       <c r="N46" t="n">
         <v>140</v>
@@ -2562,78 +2562,78 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.627</v>
+        <v>0.5504</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4089</v>
+        <v>0.3589</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3388</v>
+        <v>-0.368</v>
       </c>
       <c r="E47" t="n">
-        <v>0.627</v>
+        <v>0.5504</v>
       </c>
       <c r="F47" t="n">
-        <v>0.627</v>
+        <v>0.6722</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.627</v>
+        <v>0.6722</v>
       </c>
       <c r="I47" t="n">
-        <v>0.627</v>
+        <v>0.6722</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.627</v>
+        <v>0.6722</v>
       </c>
       <c r="N47" t="n">
-        <v>75</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5787</v>
+        <v>0.5194</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3774</v>
+        <v>0.3387</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3608</v>
+        <v>-0.3818</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5787</v>
+        <v>0.5194</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5787</v>
+        <v>0.4189</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5787</v>
+        <v>0.4189</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5787</v>
+        <v>0.4189</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5787</v>
+        <v>0.4189</v>
       </c>
       <c r="N48" t="n">
         <v>189</v>
@@ -2654,369 +2654,369 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5093</v>
+        <v>0.4944</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3321</v>
+        <v>0.3224</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3924</v>
+        <v>-0.393</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5093</v>
+        <v>0.4944</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5093</v>
+        <v>0.5779</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5093</v>
+        <v>0.5779</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5224</v>
+        <v>0.5779</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5224</v>
+        <v>0.5779</v>
       </c>
       <c r="N49" t="n">
-        <v>209</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4066</v>
+        <v>0.4631</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2652</v>
+        <v>0.302</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4391</v>
+        <v>-0.407</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4066</v>
+        <v>0.4631</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4066</v>
+        <v>0.5001</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4066</v>
+        <v>0.5001</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4066</v>
+        <v>0.513</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4066</v>
+        <v>0.513</v>
       </c>
       <c r="N50" t="n">
-        <v>189</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3279</v>
+        <v>0.3669</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2138</v>
+        <v>0.2393</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4749</v>
+        <v>-0.4499</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3279</v>
+        <v>0.3669</v>
       </c>
       <c r="F51" t="n">
-        <v>1.1273</v>
+        <v>0.2766</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.7994</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.1273</v>
+        <v>0.2766</v>
       </c>
       <c r="I51" t="n">
-        <v>1.1273</v>
+        <v>0.2766</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.7994</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="L51" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3279</v>
+        <v>0.2766</v>
       </c>
       <c r="N51" t="n">
-        <v>191</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.2763</v>
+        <v>0.3092</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1802</v>
+        <v>0.2016</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4984</v>
+        <v>-0.4757</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2763</v>
+        <v>0.3092</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2763</v>
+        <v>0.1626</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2763</v>
+        <v>0.1626</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2763</v>
+        <v>0.1626</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2763</v>
+        <v>0.1626</v>
       </c>
       <c r="N52" t="n">
-        <v>140</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.2271</v>
+        <v>0.2597</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1481</v>
+        <v>0.1694</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5208</v>
+        <v>-0.4978</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2271</v>
+        <v>0.2597</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2271</v>
+        <v>1.127</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.7901</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2271</v>
+        <v>1.127</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2271</v>
+        <v>1.127</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.7901</v>
       </c>
       <c r="K53" t="n">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2271</v>
+        <v>0.3369</v>
       </c>
       <c r="N53" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1911</v>
+        <v>0.2332</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1246</v>
+        <v>0.1521</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5372</v>
+        <v>-0.5097</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1911</v>
+        <v>0.2332</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1911</v>
+        <v>0.0134</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1911</v>
+        <v>0.0134</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1911</v>
+        <v>0.0134</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1911</v>
+        <v>0.0134</v>
       </c>
       <c r="N54" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1626</v>
+        <v>0.1667</v>
       </c>
       <c r="C55" t="n">
-        <v>0.106</v>
+        <v>0.1087</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5502</v>
+        <v>-0.5394</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1626</v>
+        <v>0.1667</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1626</v>
+        <v>0.1341</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1626</v>
+        <v>0.1341</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1626</v>
+        <v>0.1341</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1626</v>
+        <v>0.1341</v>
       </c>
       <c r="N55" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1343</v>
+        <v>0.1167</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0876</v>
+        <v>0.0761</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5631</v>
+        <v>-0.5617</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1343</v>
+        <v>0.1167</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1343</v>
+        <v>0.2261</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1343</v>
+        <v>0.2261</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1343</v>
+        <v>0.2261</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1343</v>
+        <v>0.2261</v>
       </c>
       <c r="N56" t="n">
-        <v>86</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57">
@@ -3026,31 +3026,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1319</v>
+        <v>0.0862</v>
       </c>
       <c r="C57" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0562</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5642</v>
+        <v>-0.5753</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1319</v>
+        <v>0.0862</v>
       </c>
       <c r="F57" t="n">
-        <v>0.5588</v>
+        <v>0.5585</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.4269</v>
+        <v>-0.427</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5588</v>
+        <v>0.5585</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5588</v>
+        <v>0.5585</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.4269</v>
+        <v>-0.427</v>
       </c>
       <c r="K57" t="n">
         <v>152</v>
@@ -3059,7 +3059,7 @@
         <v>39</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1319</v>
+        <v>0.1315</v>
       </c>
       <c r="N57" t="n">
         <v>191</v>
@@ -3068,78 +3068,78 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0516</v>
+        <v>0.0465</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5881</v>
+        <v>-0.582</v>
       </c>
       <c r="E58" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="F58" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.2004</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.2004</v>
       </c>
       <c r="I58" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.2004</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.2004</v>
       </c>
       <c r="N58" t="n">
-        <v>128</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0134</v>
+        <v>-0.1144</v>
       </c>
       <c r="C59" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0746</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6181</v>
+        <v>-0.6649</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0134</v>
+        <v>-0.1144</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0134</v>
+        <v>-0.0526</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0134</v>
+        <v>-0.0526</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0134</v>
+        <v>-0.0526</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0134</v>
+        <v>-0.0526</v>
       </c>
       <c r="N59" t="n">
         <v>128</v>
@@ -3160,32 +3160,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.0526</v>
+        <v>-0.2147</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0343</v>
+        <v>-0.14</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6481</v>
+        <v>-0.7097</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0526</v>
+        <v>-0.2147</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.0526</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.0526</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0526</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.0526</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="N60" t="n">
         <v>128</v>
@@ -3206,553 +3206,553 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.0756</v>
+        <v>-0.247</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0493</v>
+        <v>-0.1611</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6586</v>
+        <v>-0.7241</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.0756</v>
+        <v>-0.247</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.1069</v>
+        <v>-0.6294</v>
       </c>
       <c r="G61" t="n">
-        <v>2.0313</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.1069</v>
+        <v>-0.6294</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1377</v>
+        <v>-0.6294</v>
       </c>
       <c r="J61" t="n">
-        <v>2.0313</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="L61" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8935999999999999</v>
+        <v>-0.6294</v>
       </c>
       <c r="N61" t="n">
-        <v>282</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.2797</v>
+        <v>-0.3001</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1824</v>
+        <v>-0.1957</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.7479</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.2797</v>
+        <v>-0.3001</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2797</v>
+        <v>-2.106</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2.0093</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2797</v>
+        <v>-2.106</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2797</v>
+        <v>-1.1372</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>2.0093</v>
       </c>
       <c r="K62" t="n">
-        <v>196</v>
+        <v>121</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.2797</v>
+        <v>0.8721000000000001</v>
       </c>
       <c r="N62" t="n">
-        <v>196</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.375</v>
+        <v>-0.4453</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2445</v>
+        <v>-0.2904</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.8127</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.375</v>
+        <v>-0.4453</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.2534</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8784</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.2534</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.2534</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8784</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="L63" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3750000000000001</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="N63" t="n">
-        <v>372</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.5244</v>
+        <v>-0.4818</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.342</v>
+        <v>-0.3142</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8629</v>
+        <v>-0.829</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5244</v>
+        <v>-0.4818</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.5244</v>
+        <v>-0.308</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5244</v>
+        <v>-0.308</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5244</v>
+        <v>-0.308</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.5244</v>
+        <v>-0.308</v>
       </c>
       <c r="N64" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.6202</v>
+        <v>-0.5426</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4044</v>
+        <v>-0.3538</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9065</v>
+        <v>-0.8562</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6202</v>
+        <v>-0.5426</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.6202</v>
+        <v>-0.5246</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6202</v>
+        <v>-0.5246</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6202</v>
+        <v>-0.5246</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.6202</v>
+        <v>-0.5246</v>
       </c>
       <c r="N65" t="n">
-        <v>75</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6294</v>
+        <v>-0.5945</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4104</v>
+        <v>-0.3877</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9107</v>
+        <v>-0.8794</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6294</v>
+        <v>-0.5945</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.6294</v>
+        <v>-1.234</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.8781</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.6294</v>
+        <v>-1.234</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6294</v>
+        <v>-1.234</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>0.8781</v>
       </c>
       <c r="K66" t="n">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.6294</v>
+        <v>-0.3559</v>
       </c>
       <c r="N66" t="n">
-        <v>75</v>
+        <v>372</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bart4k</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.6997</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4164</v>
+        <v>-0.4563</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9149</v>
+        <v>-0.9264</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.6997</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.6202</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.6202</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.6202</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.6202</v>
       </c>
       <c r="N67" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Bart4k</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7131</v>
+        <v>-0.7391</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.465</v>
+        <v>-0.482</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9488</v>
+        <v>-0.944</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7131</v>
+        <v>-0.7391</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.0488</v>
+        <v>-0.6389</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.6643</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.0488</v>
+        <v>-0.6389</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0513</v>
+        <v>-0.6389</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.6643</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>178</v>
+        <v>86</v>
       </c>
       <c r="L68" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7156</v>
+        <v>-0.6389</v>
       </c>
       <c r="N68" t="n">
-        <v>215</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.9014</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4743</v>
+        <v>-0.5878</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9553</v>
+        <v>-1.0165</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.9014</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.0484</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.6643</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.0484</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.0509</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.6643</v>
       </c>
       <c r="K69" t="n">
-        <v>75</v>
+        <v>178</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.7152000000000001</v>
       </c>
       <c r="N69" t="n">
-        <v>75</v>
+        <v>215</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.0045</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5591</v>
+        <v>-0.6551</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0145</v>
+        <v>-1.0625</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.0045</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.9097</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.9097</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.9097</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.9097</v>
       </c>
       <c r="N70" t="n">
-        <v>152</v>
+        <v>252</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9104</v>
+        <v>-1.0114</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5937</v>
+        <v>-0.6596</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0386</v>
+        <v>-1.0656</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9104</v>
+        <v>-1.0114</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9104</v>
+        <v>-0.1495</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>-0.7619</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9104</v>
+        <v>-0.1495</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9104</v>
+        <v>-0.1573</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>-0.7619</v>
       </c>
       <c r="K71" t="n">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9104</v>
+        <v>-0.9192</v>
       </c>
       <c r="N71" t="n">
-        <v>252</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9123</v>
+        <v>-1.0339</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5949</v>
+        <v>-0.6742</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0395</v>
+        <v>-1.0756</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9123</v>
+        <v>-1.0339</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.1504</v>
+        <v>-0.8589</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.7619</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.1504</v>
+        <v>-0.8589</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1583</v>
+        <v>-0.8589</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.7619</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="L72" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9202</v>
+        <v>-0.8589</v>
       </c>
       <c r="N72" t="n">
-        <v>215</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73">
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9759</v>
+        <v>-1.0475</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6364</v>
+        <v>-0.6831</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0685</v>
+        <v>-1.0817</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.9759</v>
+        <v>-1.0475</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.9759</v>
+        <v>-0.9565</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.9759</v>
+        <v>-0.9565</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.9759</v>
+        <v>-0.9565</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.9759</v>
+        <v>-0.9565</v>
       </c>
       <c r="N73" t="n">
         <v>86</v>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0317</v>
+        <v>-1.0508</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6728</v>
+        <v>-0.6852</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0939</v>
+        <v>-1.0832</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0317</v>
+        <v>-1.0508</v>
       </c>
       <c r="F74" t="n">
         <v>-1.0317</v>
@@ -3850,139 +3850,139 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>chayJESUS</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.1039</v>
+        <v>-1.1017</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7199</v>
+        <v>-0.7184</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1267</v>
+        <v>-1.1059</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1039</v>
+        <v>-1.1017</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.1039</v>
+        <v>-1.1983</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.1039</v>
+        <v>-1.1983</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1039</v>
+        <v>-1.1983</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.1039</v>
+        <v>-1.1983</v>
       </c>
       <c r="N75" t="n">
-        <v>196</v>
+        <v>104</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.1797</v>
+        <v>-1.1973</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7693</v>
+        <v>-0.7808</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1612</v>
+        <v>-1.1486</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.1797</v>
+        <v>-1.1973</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.1958</v>
+        <v>-1.1319</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0161</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.1958</v>
+        <v>-1.1319</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.1958</v>
+        <v>-1.1319</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0161</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="L76" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.1797</v>
+        <v>-1.1319</v>
       </c>
       <c r="N76" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>chayJESUS</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.1983</v>
+        <v>-1.4163</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7814</v>
+        <v>-0.9236</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1697</v>
+        <v>-1.2465</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.1983</v>
+        <v>-1.4163</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.1983</v>
+        <v>-1.1792</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>0.0159</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.1983</v>
+        <v>-1.1792</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1983</v>
+        <v>-1.1792</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>0.0159</v>
       </c>
       <c r="K77" t="n">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.1983</v>
+        <v>-1.1633</v>
       </c>
       <c r="N77" t="n">
-        <v>104</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78">
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.3616</v>
+        <v>-1.8606</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8879</v>
+        <v>-1.2133</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.244</v>
+        <v>-1.4449</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.3616</v>
+        <v>-1.8606</v>
       </c>
       <c r="F78" t="n">
         <v>-1.3616</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.7582</v>
+        <v>-2.2681</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.1466</v>
+        <v>-1.4791</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4246</v>
+        <v>-1.6269</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.7582</v>
+        <v>-2.2681</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.7582</v>
+        <v>-1.7587</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.7582</v>
+        <v>-1.7587</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.7582</v>
+        <v>-1.7587</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.7582</v>
+        <v>-1.7587</v>
       </c>
       <c r="N79" t="n">
         <v>86</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2</v>
+        <v>-2.7031</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.3042</v>
+        <v>-1.7627</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5346</v>
+        <v>-1.8212</v>
       </c>
       <c r="E80" t="n">
-        <v>-2</v>
+        <v>-2.7031</v>
       </c>
       <c r="F80" t="n">
         <v>-2</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.4467</v>
+        <v>-2.7152</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.5955</v>
+        <v>-1.7706</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.738</v>
+        <v>-1.8266</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.4467</v>
+        <v>-2.7152</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.6316</v>
+        <v>-1.6314</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.8151</v>
+        <v>-0.8152</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.6316</v>
+        <v>-1.6314</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.761</v>
+        <v>-1.7608</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.8151</v>
+        <v>-0.8152</v>
       </c>
       <c r="K81" t="n">
         <v>217</v>
@@ -4163,7 +4163,7 @@
         <v>99</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.5761</v>
+        <v>-2.576</v>
       </c>
       <c r="N81" t="n">
         <v>316</v>
@@ -4269,10 +4269,10 @@
         <v>0.65</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3358</v>
+        <v>-0.3363</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.3654</v>
+        <v>-4.3719</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.55</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4283</v>
+        <v>-0.4286</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.5679</v>
+        <v>-5.5718</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.53</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4447</v>
+        <v>-0.4448</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.7811</v>
+        <v>-5.7824</v>
       </c>
     </row>
     <row r="5">
@@ -4386,13 +4386,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4697</v>
+        <v>-0.4614</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.1061</v>
+        <v>-5.9982</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.43</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5309</v>
+        <v>-0.5312</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.9017</v>
+        <v>-6.9056</v>
       </c>
     </row>
     <row r="7">
@@ -4506,7 +4506,7 @@
         <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="I8" t="n">
         <v>1.8453</v>
@@ -4549,10 +4549,10 @@
         <v>1.64</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2943</v>
+        <v>1.2945</v>
       </c>
       <c r="J9" t="n">
-        <v>16.8259</v>
+        <v>16.8285</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>1.47</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0029</v>
+        <v>1.0031</v>
       </c>
       <c r="J10" t="n">
-        <v>13.0377</v>
+        <v>13.0403</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2467</v>
+        <v>-0.2465</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.2071</v>
+        <v>-3.2045</v>
       </c>
     </row>
     <row r="12">
@@ -6069,10 +6069,10 @@
         <v>1.82</v>
       </c>
       <c r="I47" t="n">
-        <v>1.6409</v>
+        <v>1.642</v>
       </c>
       <c r="J47" t="n">
-        <v>32.818</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="48">
@@ -6106,13 +6106,13 @@
         <v>20</v>
       </c>
       <c r="H48" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I48" t="n">
-        <v>1.081</v>
+        <v>1.0636</v>
       </c>
       <c r="J48" t="n">
-        <v>21.62</v>
+        <v>21.272</v>
       </c>
     </row>
     <row r="49">
@@ -6146,13 +6146,13 @@
         <v>20</v>
       </c>
       <c r="H49" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4903</v>
+        <v>0.4681</v>
       </c>
       <c r="J49" t="n">
-        <v>9.805999999999999</v>
+        <v>9.362</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.03</v>
       </c>
       <c r="I50" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0906</v>
       </c>
       <c r="J50" t="n">
-        <v>1.798</v>
+        <v>1.812</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.91</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3673</v>
+        <v>-0.3667</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.346</v>
+        <v>-7.334</v>
       </c>
     </row>
     <row r="52">
@@ -7269,10 +7269,10 @@
         <v>1.39</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6636</v>
+        <v>0.6631</v>
       </c>
       <c r="J77" t="n">
-        <v>15.2628</v>
+        <v>15.2513</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.26</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5127</v>
+        <v>0.5123</v>
       </c>
       <c r="J78" t="n">
-        <v>11.7921</v>
+        <v>11.7829</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.93</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1099</v>
+        <v>-0.1101</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.5277</v>
+        <v>-2.5323</v>
       </c>
     </row>
     <row r="80">
@@ -7386,13 +7386,13 @@
         <v>23</v>
       </c>
       <c r="H80" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3459</v>
+        <v>-0.3368</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.9557</v>
+        <v>-7.7464</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.62</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.418</v>
+        <v>-0.4181</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.614000000000001</v>
+        <v>-9.616300000000001</v>
       </c>
     </row>
     <row r="82">
@@ -8066,13 +8066,13 @@
         <v>23</v>
       </c>
       <c r="H97" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1066</v>
+        <v>1.1195</v>
       </c>
       <c r="J97" t="n">
-        <v>25.4518</v>
+        <v>25.7485</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.22</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5548</v>
+        <v>0.5546</v>
       </c>
       <c r="J98" t="n">
-        <v>12.7604</v>
+        <v>12.7558</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>1.16</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4556</v>
+        <v>0.4555</v>
       </c>
       <c r="J99" t="n">
-        <v>10.4788</v>
+        <v>10.4765</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0837</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>-1.9251</v>
+        <v>-1.9343</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.76</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7063</v>
+        <v>-0.7066</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.2449</v>
+        <v>-16.2518</v>
       </c>
     </row>
     <row r="102">
@@ -8469,10 +8469,10 @@
         <v>1.22</v>
       </c>
       <c r="I107" t="n">
-        <v>0.478</v>
+        <v>0.4775</v>
       </c>
       <c r="J107" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>0.96</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0669</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.338</v>
+        <v>-1.342</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.92</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1176</v>
+        <v>-0.1177</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.352</v>
+        <v>-2.354</v>
       </c>
     </row>
     <row r="110">
@@ -8586,13 +8586,13 @@
         <v>20</v>
       </c>
       <c r="H110" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3023</v>
+        <v>-0.293</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.046</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.73</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3117</v>
+        <v>-0.3119</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.234</v>
+        <v>-6.238</v>
       </c>
     </row>
     <row r="112">
@@ -10269,10 +10269,10 @@
         <v>1.42</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8454</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="J152" t="n">
-        <v>14.3718</v>
+        <v>14.3004</v>
       </c>
     </row>
     <row r="153">
@@ -10306,13 +10306,13 @@
         <v>17</v>
       </c>
       <c r="H153" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1787</v>
+        <v>-0.1473</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.0379</v>
+        <v>-2.5041</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.82</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2184</v>
+        <v>-0.2191</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.7128</v>
+        <v>-3.7247</v>
       </c>
     </row>
     <row r="155">
@@ -10386,13 +10386,13 @@
         <v>17</v>
       </c>
       <c r="H155" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4496</v>
+        <v>-0.4416</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.6432</v>
+        <v>-7.5072</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.57</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4496</v>
+        <v>-0.4504</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.6432</v>
+        <v>-7.6568</v>
       </c>
     </row>
     <row r="157">
@@ -11069,10 +11069,10 @@
         <v>1.71</v>
       </c>
       <c r="I172" t="n">
-        <v>1.333</v>
+        <v>1.3333</v>
       </c>
       <c r="J172" t="n">
-        <v>23.994</v>
+        <v>23.9994</v>
       </c>
     </row>
     <row r="173">
@@ -11106,13 +11106,13 @@
         <v>18</v>
       </c>
       <c r="H173" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I173" t="n">
-        <v>1.2207</v>
+        <v>1.2084</v>
       </c>
       <c r="J173" t="n">
-        <v>21.9726</v>
+        <v>21.7512</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>1.57</v>
       </c>
       <c r="I174" t="n">
-        <v>1.1574</v>
+        <v>1.1576</v>
       </c>
       <c r="J174" t="n">
-        <v>20.8332</v>
+        <v>20.8368</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>1.21</v>
       </c>
       <c r="I175" t="n">
-        <v>0.534</v>
+        <v>0.5343</v>
       </c>
       <c r="J175" t="n">
-        <v>9.612</v>
+        <v>9.6174</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>1.08</v>
       </c>
       <c r="I176" t="n">
-        <v>0.2188</v>
+        <v>0.2191</v>
       </c>
       <c r="J176" t="n">
-        <v>3.9384</v>
+        <v>3.9438</v>
       </c>
     </row>
     <row r="177">
@@ -11866,13 +11866,13 @@
         <v>22</v>
       </c>
       <c r="H192" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I192" t="n">
-        <v>0.461</v>
+        <v>0.4782</v>
       </c>
       <c r="J192" t="n">
-        <v>10.142</v>
+        <v>10.5204</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.14</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3683</v>
+        <v>0.3676</v>
       </c>
       <c r="J193" t="n">
-        <v>8.102600000000001</v>
+        <v>8.087199999999999</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.74</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2959</v>
+        <v>-0.2961</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.5098</v>
+        <v>-6.5142</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.66</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3698</v>
+        <v>-0.37</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.1356</v>
+        <v>-8.140000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.53</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4849</v>
+        <v>-0.4851</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.6678</v>
+        <v>-10.6722</v>
       </c>
     </row>
     <row r="197">
@@ -12869,10 +12869,10 @@
         <v>1.76</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4722</v>
+        <v>1.4729</v>
       </c>
       <c r="J217" t="n">
-        <v>35.3328</v>
+        <v>35.3496</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.42</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0022</v>
+        <v>1.0027</v>
       </c>
       <c r="J218" t="n">
-        <v>24.0528</v>
+        <v>24.0648</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.16</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4649</v>
+        <v>0.4652</v>
       </c>
       <c r="J219" t="n">
-        <v>11.1576</v>
+        <v>11.1648</v>
       </c>
     </row>
     <row r="220">
@@ -12986,13 +12986,13 @@
         <v>24</v>
       </c>
       <c r="H220" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3401</v>
+        <v>-0.3667</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.1624</v>
+        <v>-8.800800000000001</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.39</v>
       </c>
       <c r="I221" t="n">
-        <v>-1.4447</v>
+        <v>-1.4445</v>
       </c>
       <c r="J221" t="n">
-        <v>-34.6728</v>
+        <v>-34.668</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.05</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1881</v>
+        <v>0.1874</v>
       </c>
       <c r="J222" t="n">
-        <v>4.1382</v>
+        <v>4.1228</v>
       </c>
     </row>
     <row r="223">
@@ -13106,13 +13106,13 @@
         <v>22</v>
       </c>
       <c r="H223" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0965</v>
+        <v>-0.0839</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.123</v>
+        <v>-1.8458</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.86</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1768</v>
+        <v>-0.177</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.8896</v>
+        <v>-3.894</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.65</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.376</v>
+        <v>-0.3763</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.272</v>
+        <v>-8.278600000000001</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.64</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3851</v>
+        <v>-0.3853</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.472200000000001</v>
+        <v>-8.476599999999999</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.65</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3124</v>
+        <v>1.3129</v>
       </c>
       <c r="J227" t="n">
-        <v>28.8728</v>
+        <v>28.8838</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.38</v>
       </c>
       <c r="I228" t="n">
-        <v>0.9172</v>
+        <v>0.9177</v>
       </c>
       <c r="J228" t="n">
-        <v>20.1784</v>
+        <v>20.1894</v>
       </c>
     </row>
     <row r="229">
@@ -13346,13 +13346,13 @@
         <v>22</v>
       </c>
       <c r="H229" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2877</v>
+        <v>0.261</v>
       </c>
       <c r="J229" t="n">
-        <v>6.3294</v>
+        <v>5.742</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>1.01</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0305</v>
+        <v>0.0308</v>
       </c>
       <c r="J230" t="n">
-        <v>0.671</v>
+        <v>0.6776</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7335</v>
+        <v>-0.7331</v>
       </c>
       <c r="J231" t="n">
-        <v>-16.137</v>
+        <v>-16.1282</v>
       </c>
     </row>
     <row r="232">
@@ -14069,10 +14069,10 @@
         <v>1.83</v>
       </c>
       <c r="I247" t="n">
-        <v>1.544</v>
+        <v>1.5447</v>
       </c>
       <c r="J247" t="n">
-        <v>30.88</v>
+        <v>30.894</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.42</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.9889</v>
       </c>
       <c r="J248" t="n">
-        <v>19.768</v>
+        <v>19.778</v>
       </c>
     </row>
     <row r="249">
@@ -14146,13 +14146,13 @@
         <v>20</v>
       </c>
       <c r="H249" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="I249" t="n">
-        <v>0.695</v>
+        <v>0.6746</v>
       </c>
       <c r="J249" t="n">
-        <v>13.9</v>
+        <v>13.492</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5992</v>
+        <v>-0.5989</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.984</v>
+        <v>-11.978</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.58</v>
       </c>
       <c r="I251" t="n">
-        <v>-1.0873</v>
+        <v>-1.087</v>
       </c>
       <c r="J251" t="n">
-        <v>-21.746</v>
+        <v>-21.74</v>
       </c>
     </row>
     <row r="252">
@@ -15469,10 +15469,10 @@
         <v>1.45</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5961</v>
+        <v>0.5965</v>
       </c>
       <c r="J282" t="n">
-        <v>14.3064</v>
+        <v>14.316</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.41</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5533</v>
       </c>
       <c r="J283" t="n">
-        <v>13.2696</v>
+        <v>13.2792</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.96</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.0781</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.8792</v>
+        <v>-1.8744</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2489</v>
+        <v>-0.2488</v>
       </c>
       <c r="J285" t="n">
-        <v>-5.9736</v>
+        <v>-5.9712</v>
       </c>
     </row>
     <row r="286">
@@ -15626,13 +15626,13 @@
         <v>24</v>
       </c>
       <c r="H286" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3168</v>
+        <v>-0.326</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.6032</v>
+        <v>-7.824</v>
       </c>
     </row>
     <row r="287">
@@ -17469,10 +17469,10 @@
         <v>1.34</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6546</v>
+        <v>0.654</v>
       </c>
       <c r="J332" t="n">
-        <v>18.9834</v>
+        <v>18.966</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.24</v>
       </c>
       <c r="I333" t="n">
-        <v>0.4963</v>
+        <v>0.4958</v>
       </c>
       <c r="J333" t="n">
-        <v>14.3927</v>
+        <v>14.3782</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>0.98</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.0439</v>
+        <v>-0.044</v>
       </c>
       <c r="J334" t="n">
-        <v>-1.2731</v>
+        <v>-1.276</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.79</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2639</v>
+        <v>-0.2641</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.6531</v>
+        <v>-7.6589</v>
       </c>
     </row>
     <row r="336">
@@ -17626,13 +17626,13 @@
         <v>29</v>
       </c>
       <c r="H336" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.312</v>
+        <v>-0.3027</v>
       </c>
       <c r="J336" t="n">
-        <v>-9.048</v>
+        <v>-8.7783</v>
       </c>
     </row>
     <row r="337">
@@ -17666,13 +17666,13 @@
         <v>29</v>
       </c>
       <c r="H337" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9813</v>
+        <v>0.9979</v>
       </c>
       <c r="J337" t="n">
-        <v>28.4577</v>
+        <v>28.9391</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.31</v>
       </c>
       <c r="I338" t="n">
-        <v>0.786</v>
+        <v>0.7855</v>
       </c>
       <c r="J338" t="n">
-        <v>22.794</v>
+        <v>22.7795</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.05</v>
       </c>
       <c r="I339" t="n">
-        <v>0.1794</v>
+        <v>0.1791</v>
       </c>
       <c r="J339" t="n">
-        <v>5.2026</v>
+        <v>5.1939</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>1.05</v>
       </c>
       <c r="I340" t="n">
-        <v>0.1794</v>
+        <v>0.1791</v>
       </c>
       <c r="J340" t="n">
-        <v>5.2026</v>
+        <v>5.1939</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.89</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.396</v>
+        <v>-0.3964</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.484</v>
+        <v>-11.4956</v>
       </c>
     </row>
     <row r="342">
@@ -18269,10 +18269,10 @@
         <v>1.4</v>
       </c>
       <c r="I352" t="n">
-        <v>0.7437</v>
+        <v>0.7443</v>
       </c>
       <c r="J352" t="n">
-        <v>17.1051</v>
+        <v>17.1189</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.15</v>
       </c>
       <c r="I353" t="n">
-        <v>0.3414</v>
+        <v>0.3418</v>
       </c>
       <c r="J353" t="n">
-        <v>7.8522</v>
+        <v>7.8614</v>
       </c>
     </row>
     <row r="354">
@@ -18346,13 +18346,13 @@
         <v>23</v>
       </c>
       <c r="H354" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I354" t="n">
-        <v>0.2676</v>
+        <v>0.2487</v>
       </c>
       <c r="J354" t="n">
-        <v>6.1548</v>
+        <v>5.7201</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>0.97</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.0599</v>
+        <v>-0.0598</v>
       </c>
       <c r="J355" t="n">
-        <v>-1.3777</v>
+        <v>-1.3754</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.49</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.533</v>
+        <v>-0.5329</v>
       </c>
       <c r="J356" t="n">
-        <v>-12.259</v>
+        <v>-12.2567</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.46</v>
       </c>
       <c r="I357" t="n">
-        <v>1.0632</v>
+        <v>1.0627</v>
       </c>
       <c r="J357" t="n">
-        <v>24.4536</v>
+        <v>24.4421</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.13</v>
       </c>
       <c r="I358" t="n">
-        <v>0.3945</v>
+        <v>0.3943</v>
       </c>
       <c r="J358" t="n">
-        <v>9.073499999999999</v>
+        <v>9.068899999999999</v>
       </c>
     </row>
     <row r="359">
@@ -18546,13 +18546,13 @@
         <v>23</v>
       </c>
       <c r="H359" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I359" t="n">
-        <v>0.2108</v>
+        <v>0.2393</v>
       </c>
       <c r="J359" t="n">
-        <v>4.8484</v>
+        <v>5.5039</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>1.04</v>
       </c>
       <c r="I360" t="n">
-        <v>0.1492</v>
+        <v>0.1489</v>
       </c>
       <c r="J360" t="n">
-        <v>3.4316</v>
+        <v>3.4247</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.98</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.123</v>
+        <v>-0.1234</v>
       </c>
       <c r="J361" t="n">
-        <v>-2.829</v>
+        <v>-2.8382</v>
       </c>
     </row>
     <row r="362">
@@ -20869,10 +20869,10 @@
         <v>2.05</v>
       </c>
       <c r="I417" t="n">
-        <v>1.7558</v>
+        <v>1.7564</v>
       </c>
       <c r="J417" t="n">
-        <v>31.6044</v>
+        <v>31.6152</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.58</v>
       </c>
       <c r="I418" t="n">
-        <v>1.179</v>
+        <v>1.1793</v>
       </c>
       <c r="J418" t="n">
-        <v>21.222</v>
+        <v>21.2274</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>1.28</v>
       </c>
       <c r="I419" t="n">
-        <v>0.6907</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J419" t="n">
-        <v>12.4326</v>
+        <v>12.438</v>
       </c>
     </row>
     <row r="420">
@@ -20986,13 +20986,13 @@
         <v>18</v>
       </c>
       <c r="H420" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="I420" t="n">
-        <v>0.4992</v>
+        <v>0.4769</v>
       </c>
       <c r="J420" t="n">
-        <v>8.9856</v>
+        <v>8.584199999999999</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.77</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.7189</v>
+        <v>-0.7186</v>
       </c>
       <c r="J421" t="n">
-        <v>-12.9402</v>
+        <v>-12.9348</v>
       </c>
     </row>
     <row r="422">
@@ -21066,13 +21066,13 @@
         <v>19</v>
       </c>
       <c r="H422" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I422" t="n">
-        <v>1.6787</v>
+        <v>1.6672</v>
       </c>
       <c r="J422" t="n">
-        <v>31.8953</v>
+        <v>31.6768</v>
       </c>
     </row>
     <row r="423">
@@ -21109,10 +21109,10 @@
         <v>1.43</v>
       </c>
       <c r="I423" t="n">
-        <v>0.98</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J423" t="n">
-        <v>18.62</v>
+        <v>18.6257</v>
       </c>
     </row>
     <row r="424">
@@ -21149,10 +21149,10 @@
         <v>1.09</v>
       </c>
       <c r="I424" t="n">
-        <v>0.2661</v>
+        <v>0.2664</v>
       </c>
       <c r="J424" t="n">
-        <v>5.0559</v>
+        <v>5.0616</v>
       </c>
     </row>
     <row r="425">
@@ -21189,10 +21189,10 @@
         <v>1.05</v>
       </c>
       <c r="I425" t="n">
-        <v>0.1514</v>
+        <v>0.1517</v>
       </c>
       <c r="J425" t="n">
-        <v>2.8766</v>
+        <v>2.8823</v>
       </c>
     </row>
     <row r="426">
@@ -21229,10 +21229,10 @@
         <v>1</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.0518</v>
+        <v>-0.0515</v>
       </c>
       <c r="J426" t="n">
-        <v>-0.9842</v>
+        <v>-0.9785</v>
       </c>
     </row>
     <row r="427">
@@ -22066,13 +22066,13 @@
         <v>16</v>
       </c>
       <c r="H447" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I447" t="n">
-        <v>0.1687</v>
+        <v>0.1878</v>
       </c>
       <c r="J447" t="n">
-        <v>2.6992</v>
+        <v>3.0048</v>
       </c>
     </row>
     <row r="448">
@@ -22109,10 +22109,10 @@
         <v>0.78</v>
       </c>
       <c r="I448" t="n">
-        <v>-0.2427</v>
+        <v>-0.243</v>
       </c>
       <c r="J448" t="n">
-        <v>-3.8832</v>
+        <v>-3.888</v>
       </c>
     </row>
     <row r="449">
@@ -22149,10 +22149,10 @@
         <v>0.7</v>
       </c>
       <c r="I449" t="n">
-        <v>-0.3175</v>
+        <v>-0.3176</v>
       </c>
       <c r="J449" t="n">
-        <v>-5.08</v>
+        <v>-5.0816</v>
       </c>
     </row>
     <row r="450">
@@ -22189,10 +22189,10 @@
         <v>0.67</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.3436</v>
+        <v>-0.3439</v>
       </c>
       <c r="J450" t="n">
-        <v>-5.4976</v>
+        <v>-5.5024</v>
       </c>
     </row>
     <row r="451">
@@ -22229,10 +22229,10 @@
         <v>0.31</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.6584</v>
+        <v>-0.6586</v>
       </c>
       <c r="J451" t="n">
-        <v>-10.5344</v>
+        <v>-10.5376</v>
       </c>
     </row>
     <row r="452">
@@ -22669,10 +22669,10 @@
         <v>1.24</v>
       </c>
       <c r="I462" t="n">
-        <v>0.5239</v>
+        <v>0.5246</v>
       </c>
       <c r="J462" t="n">
-        <v>24.6233</v>
+        <v>24.6562</v>
       </c>
     </row>
     <row r="463">
@@ -22706,13 +22706,13 @@
         <v>47</v>
       </c>
       <c r="H463" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I463" t="n">
-        <v>0.2896</v>
+        <v>0.2702</v>
       </c>
       <c r="J463" t="n">
-        <v>13.6112</v>
+        <v>12.6994</v>
       </c>
     </row>
     <row r="464">
@@ -22749,10 +22749,10 @@
         <v>0.93</v>
       </c>
       <c r="I464" t="n">
-        <v>-0.1062</v>
+        <v>-0.1061</v>
       </c>
       <c r="J464" t="n">
-        <v>-4.9914</v>
+        <v>-4.9867</v>
       </c>
     </row>
     <row r="465">
@@ -22789,10 +22789,10 @@
         <v>0.72</v>
       </c>
       <c r="I465" t="n">
-        <v>-0.3216</v>
+        <v>-0.3214</v>
       </c>
       <c r="J465" t="n">
-        <v>-15.1152</v>
+        <v>-15.1058</v>
       </c>
     </row>
     <row r="466">
@@ -22829,10 +22829,10 @@
         <v>0.6</v>
       </c>
       <c r="I466" t="n">
-        <v>-0.4302</v>
+        <v>-0.4301</v>
       </c>
       <c r="J466" t="n">
-        <v>-20.2194</v>
+        <v>-20.2147</v>
       </c>
     </row>
     <row r="467">
@@ -23869,10 +23869,10 @@
         <v>1.49</v>
       </c>
       <c r="I492" t="n">
-        <v>0.8915</v>
+        <v>0.8893</v>
       </c>
       <c r="J492" t="n">
-        <v>25.8535</v>
+        <v>25.7897</v>
       </c>
     </row>
     <row r="493">
@@ -23909,10 +23909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I493" t="n">
-        <v>-0.0975</v>
+        <v>-0.0979</v>
       </c>
       <c r="J493" t="n">
-        <v>-2.8275</v>
+        <v>-2.8391</v>
       </c>
     </row>
     <row r="494">
@@ -23946,13 +23946,13 @@
         <v>29</v>
       </c>
       <c r="H494" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="I494" t="n">
-        <v>-0.2101</v>
+        <v>-0.1789</v>
       </c>
       <c r="J494" t="n">
-        <v>-6.0929</v>
+        <v>-5.1881</v>
       </c>
     </row>
     <row r="495">
@@ -23989,10 +23989,10 @@
         <v>0.83</v>
       </c>
       <c r="I495" t="n">
-        <v>-0.2204</v>
+        <v>-0.2209</v>
       </c>
       <c r="J495" t="n">
-        <v>-6.3916</v>
+        <v>-6.4061</v>
       </c>
     </row>
     <row r="496">
@@ -24029,10 +24029,10 @@
         <v>0.8</v>
       </c>
       <c r="I496" t="n">
-        <v>-0.2506</v>
+        <v>-0.2511</v>
       </c>
       <c r="J496" t="n">
-        <v>-7.2674</v>
+        <v>-7.2819</v>
       </c>
     </row>
     <row r="497">
@@ -24066,13 +24066,13 @@
         <v>29</v>
       </c>
       <c r="H497" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I497" t="n">
-        <v>1.1827</v>
+        <v>1.1705</v>
       </c>
       <c r="J497" t="n">
-        <v>34.2983</v>
+        <v>33.9445</v>
       </c>
     </row>
     <row r="498">
@@ -24109,16 +24109,16 @@
         <v>1.31</v>
       </c>
       <c r="I498" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7965</v>
       </c>
       <c r="J498" t="n">
-        <v>23.0521</v>
+        <v>23.0985</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -24146,19 +24146,19 @@
         <v>29</v>
       </c>
       <c r="H499" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I499" t="n">
-        <v>-0.2509</v>
+        <v>-0.2791</v>
       </c>
       <c r="J499" t="n">
-        <v>-7.2761</v>
+        <v>-8.0939</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -24186,13 +24186,13 @@
         <v>29</v>
       </c>
       <c r="H500" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I500" t="n">
-        <v>-0.2509</v>
+        <v>-0.2791</v>
       </c>
       <c r="J500" t="n">
-        <v>-7.2761</v>
+        <v>-8.0939</v>
       </c>
     </row>
     <row r="501">
@@ -24229,10 +24229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I501" t="n">
-        <v>-0.5859</v>
+        <v>-0.5847</v>
       </c>
       <c r="J501" t="n">
-        <v>-16.9911</v>
+        <v>-16.9563</v>
       </c>
     </row>
     <row r="502">
@@ -26269,10 +26269,10 @@
         <v>1.65</v>
       </c>
       <c r="I552" t="n">
-        <v>1.2548</v>
+        <v>1.2551</v>
       </c>
       <c r="J552" t="n">
-        <v>20.0768</v>
+        <v>20.0816</v>
       </c>
     </row>
     <row r="553">
@@ -26309,10 +26309,10 @@
         <v>1.63</v>
       </c>
       <c r="I553" t="n">
-        <v>1.2298</v>
+        <v>1.2301</v>
       </c>
       <c r="J553" t="n">
-        <v>19.6768</v>
+        <v>19.6816</v>
       </c>
     </row>
     <row r="554">
@@ -26349,10 +26349,10 @@
         <v>1.42</v>
       </c>
       <c r="I554" t="n">
-        <v>0.9457</v>
+        <v>0.9459</v>
       </c>
       <c r="J554" t="n">
-        <v>15.1312</v>
+        <v>15.1344</v>
       </c>
     </row>
     <row r="555">
@@ -26386,13 +26386,13 @@
         <v>16</v>
       </c>
       <c r="H555" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="I555" t="n">
-        <v>0.892</v>
+        <v>0.8736</v>
       </c>
       <c r="J555" t="n">
-        <v>14.272</v>
+        <v>13.9776</v>
       </c>
     </row>
     <row r="556">
@@ -26429,10 +26429,10 @@
         <v>1.23</v>
       </c>
       <c r="I556" t="n">
-        <v>0.5736</v>
+        <v>0.5739</v>
       </c>
       <c r="J556" t="n">
-        <v>9.1776</v>
+        <v>9.182399999999999</v>
       </c>
     </row>
     <row r="557">
@@ -26469,10 +26469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I557" t="n">
-        <v>-0.0295</v>
+        <v>-0.0303</v>
       </c>
       <c r="J557" t="n">
-        <v>-0.472</v>
+        <v>-0.4848</v>
       </c>
     </row>
     <row r="558">
@@ -26509,10 +26509,10 @@
         <v>0.78</v>
       </c>
       <c r="I558" t="n">
-        <v>-0.2226</v>
+        <v>-0.2231</v>
       </c>
       <c r="J558" t="n">
-        <v>-3.5616</v>
+        <v>-3.5696</v>
       </c>
     </row>
     <row r="559">
@@ -26549,10 +26549,10 @@
         <v>0.54</v>
       </c>
       <c r="I559" t="n">
-        <v>-0.4456</v>
+        <v>-0.4459</v>
       </c>
       <c r="J559" t="n">
-        <v>-7.1296</v>
+        <v>-7.1344</v>
       </c>
     </row>
     <row r="560">
@@ -26589,10 +26589,10 @@
         <v>0.4</v>
       </c>
       <c r="I560" t="n">
-        <v>-0.5688</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="J560" t="n">
-        <v>-9.1008</v>
+        <v>-9.105600000000001</v>
       </c>
     </row>
     <row r="561">
@@ -26626,13 +26626,13 @@
         <v>16</v>
       </c>
       <c r="H561" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="I561" t="n">
-        <v>-0.6041</v>
+        <v>-0.5956</v>
       </c>
       <c r="J561" t="n">
-        <v>-9.6656</v>
+        <v>-9.5296</v>
       </c>
     </row>
     <row r="562">
@@ -26669,10 +26669,10 @@
         <v>1.37</v>
       </c>
       <c r="I562" t="n">
-        <v>0.8973</v>
+        <v>0.8968</v>
       </c>
       <c r="J562" t="n">
-        <v>17.946</v>
+        <v>17.936</v>
       </c>
     </row>
     <row r="563">
@@ -26709,10 +26709,10 @@
         <v>1.3</v>
       </c>
       <c r="I563" t="n">
-        <v>0.7574</v>
+        <v>0.757</v>
       </c>
       <c r="J563" t="n">
-        <v>15.148</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="564">
@@ -26749,10 +26749,10 @@
         <v>1.13</v>
       </c>
       <c r="I564" t="n">
-        <v>0.389</v>
+        <v>0.3888</v>
       </c>
       <c r="J564" t="n">
-        <v>7.78</v>
+        <v>7.776</v>
       </c>
     </row>
     <row r="565">
@@ -26786,13 +26786,13 @@
         <v>20</v>
       </c>
       <c r="H565" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I565" t="n">
-        <v>0.2874</v>
+        <v>0.3134</v>
       </c>
       <c r="J565" t="n">
-        <v>5.748</v>
+        <v>6.268</v>
       </c>
     </row>
     <row r="566">
@@ -26829,10 +26829,10 @@
         <v>1</v>
       </c>
       <c r="I566" t="n">
-        <v>-0.0297</v>
+        <v>-0.03</v>
       </c>
       <c r="J566" t="n">
-        <v>-0.594</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="567">
@@ -28869,10 +28869,10 @@
         <v>1.52</v>
       </c>
       <c r="I617" t="n">
-        <v>1.1303</v>
+        <v>1.1307</v>
       </c>
       <c r="J617" t="n">
-        <v>32.7787</v>
+        <v>32.7903</v>
       </c>
     </row>
     <row r="618">
@@ -28909,10 +28909,10 @@
         <v>1.43</v>
       </c>
       <c r="I618" t="n">
-        <v>0.9996</v>
+        <v>1.0001</v>
       </c>
       <c r="J618" t="n">
-        <v>28.9884</v>
+        <v>29.0029</v>
       </c>
     </row>
     <row r="619">
@@ -28949,10 +28949,10 @@
         <v>1.24</v>
       </c>
       <c r="I619" t="n">
-        <v>0.6287</v>
+        <v>0.629</v>
       </c>
       <c r="J619" t="n">
-        <v>18.2323</v>
+        <v>18.241</v>
       </c>
     </row>
     <row r="620">
@@ -28989,10 +28989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I620" t="n">
-        <v>-0.2688</v>
+        <v>-0.2685</v>
       </c>
       <c r="J620" t="n">
-        <v>-7.7952</v>
+        <v>-7.7865</v>
       </c>
     </row>
     <row r="621">
@@ -29026,13 +29026,13 @@
         <v>29</v>
       </c>
       <c r="H621" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I621" t="n">
-        <v>-0.3812</v>
+        <v>-0.4072</v>
       </c>
       <c r="J621" t="n">
-        <v>-11.0548</v>
+        <v>-11.8088</v>
       </c>
     </row>
     <row r="622">
@@ -29066,13 +29066,13 @@
         <v>13</v>
       </c>
       <c r="H622" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I622" t="n">
-        <v>-0.1021</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J622" t="n">
-        <v>-1.3273</v>
+        <v>-1.2064</v>
       </c>
     </row>
     <row r="623">
@@ -29106,13 +29106,13 @@
         <v>13</v>
       </c>
       <c r="H623" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="I623" t="n">
-        <v>-0.2782</v>
+        <v>-0.2502</v>
       </c>
       <c r="J623" t="n">
-        <v>-3.6166</v>
+        <v>-3.2526</v>
       </c>
     </row>
     <row r="624">
@@ -29146,13 +29146,13 @@
         <v>13</v>
       </c>
       <c r="H624" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="I624" t="n">
-        <v>-0.457</v>
+        <v>-0.4496</v>
       </c>
       <c r="J624" t="n">
-        <v>-5.941</v>
+        <v>-5.8448</v>
       </c>
     </row>
     <row r="625">
@@ -29189,10 +29189,10 @@
         <v>0.5</v>
       </c>
       <c r="I625" t="n">
-        <v>-0.4833</v>
+        <v>-0.4848</v>
       </c>
       <c r="J625" t="n">
-        <v>-6.2829</v>
+        <v>-6.3024</v>
       </c>
     </row>
     <row r="626">
@@ -29229,10 +29229,10 @@
         <v>0.46</v>
       </c>
       <c r="I626" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.52</v>
       </c>
       <c r="J626" t="n">
-        <v>-6.7418</v>
+        <v>-6.76</v>
       </c>
     </row>
     <row r="627">
@@ -29266,7 +29266,7 @@
         <v>13</v>
       </c>
       <c r="H627" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="I627" t="n">
         <v>1.9372</v>
@@ -29306,13 +29306,13 @@
         <v>13</v>
       </c>
       <c r="H628" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="I628" t="n">
-        <v>1.9007</v>
+        <v>1.8909</v>
       </c>
       <c r="J628" t="n">
-        <v>24.7091</v>
+        <v>24.5817</v>
       </c>
     </row>
     <row r="629">
@@ -29349,10 +29349,10 @@
         <v>1.92</v>
       </c>
       <c r="I629" t="n">
-        <v>1.5384</v>
+        <v>1.539</v>
       </c>
       <c r="J629" t="n">
-        <v>19.9992</v>
+        <v>20.007</v>
       </c>
     </row>
     <row r="630">
@@ -29386,13 +29386,13 @@
         <v>13</v>
       </c>
       <c r="H630" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I630" t="n">
-        <v>1.2294</v>
+        <v>1.2178</v>
       </c>
       <c r="J630" t="n">
-        <v>15.9822</v>
+        <v>15.8314</v>
       </c>
     </row>
     <row r="631">
@@ -29429,10 +29429,10 @@
         <v>0.63</v>
       </c>
       <c r="I631" t="n">
-        <v>-1.0476</v>
+        <v>-1.0472</v>
       </c>
       <c r="J631" t="n">
-        <v>-13.6188</v>
+        <v>-13.6136</v>
       </c>
     </row>
     <row r="632">
@@ -30666,13 +30666,13 @@
         <v>23</v>
       </c>
       <c r="H662" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I662" t="n">
-        <v>0.9608</v>
+        <v>0.9429</v>
       </c>
       <c r="J662" t="n">
-        <v>22.0984</v>
+        <v>21.6867</v>
       </c>
     </row>
     <row r="663">
@@ -30709,10 +30709,10 @@
         <v>1.34</v>
       </c>
       <c r="I663" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8448</v>
       </c>
       <c r="J663" t="n">
-        <v>19.4189</v>
+        <v>19.4304</v>
       </c>
     </row>
     <row r="664">
@@ -30749,10 +30749,10 @@
         <v>1.22</v>
       </c>
       <c r="I664" t="n">
-        <v>0.5947</v>
+        <v>0.5951</v>
       </c>
       <c r="J664" t="n">
-        <v>13.6781</v>
+        <v>13.6873</v>
       </c>
     </row>
     <row r="665">
@@ -30789,10 +30789,10 @@
         <v>1.16</v>
       </c>
       <c r="I665" t="n">
-        <v>0.4619</v>
+        <v>0.4621</v>
       </c>
       <c r="J665" t="n">
-        <v>10.6237</v>
+        <v>10.6283</v>
       </c>
     </row>
     <row r="666">
@@ -30829,10 +30829,10 @@
         <v>0.64</v>
       </c>
       <c r="I666" t="n">
-        <v>-0.9621</v>
+        <v>-0.9618</v>
       </c>
       <c r="J666" t="n">
-        <v>-22.1283</v>
+        <v>-22.1214</v>
       </c>
     </row>
     <row r="667">
@@ -30866,13 +30866,13 @@
         <v>23</v>
       </c>
       <c r="H667" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I667" t="n">
-        <v>0.7257</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="J667" t="n">
-        <v>16.6911</v>
+        <v>17.0292</v>
       </c>
     </row>
     <row r="668">
@@ -30909,10 +30909,10 @@
         <v>0.99</v>
       </c>
       <c r="I668" t="n">
-        <v>-0.0215</v>
+        <v>-0.0217</v>
       </c>
       <c r="J668" t="n">
-        <v>-0.4945</v>
+        <v>-0.4991</v>
       </c>
     </row>
     <row r="669">
@@ -30949,10 +30949,10 @@
         <v>0.86</v>
       </c>
       <c r="I669" t="n">
-        <v>-0.1857</v>
+        <v>-0.1859</v>
       </c>
       <c r="J669" t="n">
-        <v>-4.2711</v>
+        <v>-4.2757</v>
       </c>
     </row>
     <row r="670">
@@ -30989,10 +30989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I670" t="n">
-        <v>-0.2371</v>
+        <v>-0.2372</v>
       </c>
       <c r="J670" t="n">
-        <v>-5.4533</v>
+        <v>-5.4556</v>
       </c>
     </row>
     <row r="671">
@@ -31029,10 +31029,10 @@
         <v>0.68</v>
       </c>
       <c r="I671" t="n">
-        <v>-0.3607</v>
+        <v>-0.3609</v>
       </c>
       <c r="J671" t="n">
-        <v>-8.296099999999999</v>
+        <v>-8.300700000000001</v>
       </c>
     </row>
     <row r="672">
@@ -31269,10 +31269,10 @@
         <v>1.27</v>
       </c>
       <c r="I677" t="n">
-        <v>0.5841</v>
+        <v>0.5849</v>
       </c>
       <c r="J677" t="n">
-        <v>12.2661</v>
+        <v>12.2829</v>
       </c>
     </row>
     <row r="678">
@@ -31309,10 +31309,10 @@
         <v>0.96</v>
       </c>
       <c r="I678" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0645</v>
       </c>
       <c r="J678" t="n">
-        <v>-1.3587</v>
+        <v>-1.3545</v>
       </c>
     </row>
     <row r="679">
@@ -31346,13 +31346,13 @@
         <v>21</v>
       </c>
       <c r="H679" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I679" t="n">
-        <v>-0.1041</v>
+        <v>-0.1159</v>
       </c>
       <c r="J679" t="n">
-        <v>-2.1861</v>
+        <v>-2.4339</v>
       </c>
     </row>
     <row r="680">
@@ -31389,10 +31389,10 @@
         <v>0.75</v>
       </c>
       <c r="I680" t="n">
-        <v>-0.2906</v>
+        <v>-0.2904</v>
       </c>
       <c r="J680" t="n">
-        <v>-6.1026</v>
+        <v>-6.0984</v>
       </c>
     </row>
     <row r="681">
@@ -31429,10 +31429,10 @@
         <v>0.55</v>
       </c>
       <c r="I681" t="n">
-        <v>-0.4713</v>
+        <v>-0.4711</v>
       </c>
       <c r="J681" t="n">
-        <v>-9.8973</v>
+        <v>-9.8931</v>
       </c>
     </row>
     <row r="682">
